--- a/workspaces/btc_daily_14days/volatility/realized_vol_7.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_7.xlsx
@@ -575,46 +575,46 @@
         <v>132</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.294440467668807</v>
+        <v>1.289541892519004</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.018244059521351</v>
+        <v>7.991673730231902</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.593397852328799</v>
+        <v>4.577996744590031</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.999402675193046</v>
+        <v>6.97602946073993</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.462275137100967</v>
+        <v>6.44054077607592</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.244742397097262</v>
+        <v>5.226895130953004</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.920012539259979</v>
+        <v>5.899878930111534</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.453579913993735</v>
+        <v>5.434928241053044</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.153096768749691</v>
+        <v>6.13199745696145</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.821329925497636</v>
+        <v>6.797942898784129</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.655872470027774</v>
+        <v>9.623133455878175</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.21231039605061</v>
+        <v>11.17438926538392</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.55370091521758</v>
+        <v>11.51453139185873</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.80728461988816</v>
+        <v>11.76726576439393</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>240</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.826771653543112</v>
+        <v>-0.8247621043310929</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3550101577270794</v>
+        <v>-0.3550332385381054</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9174197685036418</v>
+        <v>0.913300448053235</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.303215687343268</v>
+        <v>7.276450733369785</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.017641602755241</v>
+        <v>7.98831471320198</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.648825667785943</v>
+        <v>6.624301291790978</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.313903685531983</v>
+        <v>5.293874612996589</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.934635759421319</v>
+        <v>6.908958295621041</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.458077169038802</v>
+        <v>6.433808949206025</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.025569912974497</v>
+        <v>6.002624116471857</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.151195444492558</v>
+        <v>4.134385048386967</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.515608929156606</v>
+        <v>2.504230303441688</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.004983305752681133</v>
+        <v>0.00217705123366585</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.6739698147988165</v>
+        <v>0.6687809159085418</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>324</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.136191309419651</v>
+        <v>2.12721815217953</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.612204976012841</v>
+        <v>3.597027131889114</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.21825933220105</v>
+        <v>3.204670502037999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.805566733324355</v>
+        <v>1.795362884627139</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.048423145263889</v>
+        <v>4.029395748730259</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.656721643549169</v>
+        <v>4.635741804643949</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.119324126945017</v>
+        <v>6.092900558919879</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.962705704606201</v>
+        <v>5.936485644193048</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.594324090124047</v>
+        <v>5.569333635873029</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.291250072727237</v>
+        <v>6.263487804043891</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.39759156539322</v>
+        <v>6.369416829400805</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.124545442073327</v>
+        <v>6.097498861138035</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.775315602956354</v>
+        <v>4.753826314532347</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.098401406255128</v>
+        <v>4.079274743069362</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.666448700832817</v>
+        <v>-2.691206999556336</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.747348686720592</v>
+        <v>-3.780742464056551</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.608383881299886</v>
+        <v>-3.640919995454134</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.175112977655274</v>
+        <v>-4.209034421692806</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.751668012698318</v>
+        <v>-5.799905170294274</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.232683717522022</v>
+        <v>-4.264589587026336</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.089304966140311</v>
+        <v>-7.151840669675664</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.713697853265202</v>
+        <v>-7.782076430209933</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.736711268989595</v>
+        <v>-6.794065012613125</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.806662318921553</v>
+        <v>-4.841494597715936</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.436942562063699</v>
+        <v>-7.500852256034158</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.097824243963004</v>
+        <v>-8.169633750395953</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.431177770907397</v>
+        <v>-6.487193156413639</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.103676043329173</v>
+        <v>-4.133850663038643</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.458638357106324</v>
+        <v>2.498387501990393</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.028334616880301</v>
+        <v>-2.051499380213365</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.423203323476812</v>
+        <v>-2.453012149705955</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.760897685539355</v>
+        <v>-2.789335883735667</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.723365096216995</v>
+        <v>-4.778332930493157</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.789408655269021</v>
+        <v>-3.829268300372576</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.061861523170862</v>
+        <v>-3.09329264799657</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.483507499052493</v>
+        <v>-4.535223916704062</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.330482193645643</v>
+        <v>-5.393124779436206</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.401212330217419</v>
+        <v>-4.44588811266334</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.641428432767327</v>
+        <v>-3.678286884308136</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.008097000278021</v>
+        <v>-2.022531649411398</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.781089666406345</v>
+        <v>-1.793831281550965</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.178341300845666</v>
+        <v>-2.193773196645452</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>317</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.080694171903659</v>
+        <v>2.076490954458905</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.4772516808083012</v>
+        <v>-0.4769443316324242</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.764864866900226</v>
+        <v>-2.760706592023631</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.681930346280119</v>
+        <v>-7.670566762892484</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.16672380109992</v>
+        <v>-9.152917734107767</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.661079970639634</v>
+        <v>-6.651632607880615</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.960324728921378</v>
+        <v>-2.95668347479878</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.534763648207679</v>
+        <v>-1.53324991727218</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.2266783608884</v>
+        <v>-2.224091626137778</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.076803545916327</v>
+        <v>-3.073527450160107</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.860449904361609</v>
+        <v>-4.854026032835037</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.090449674873881</v>
+        <v>-6.082131189388811</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.302543925496018</v>
+        <v>-4.2969428919438</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.525780121141629</v>
+        <v>-1.524962512061755</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.493438320210039</v>
+        <v>-2.501160144951392</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.692582554643103</v>
+        <v>-2.704098775374064</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.087451261239742</v>
+        <v>-3.102780728756557</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.369627507163386</v>
+        <v>-4.391649007351688</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.602963976472779</v>
+        <v>-6.636638500313552</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.282923168700691</v>
+        <v>-8.321962629156403</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.390255756029397</v>
+        <v>-6.418591734370011</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.445009776279889</v>
+        <v>-5.468560345341828</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.788495538168405</v>
+        <v>-5.813956500782474</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-6.073648971783776</v>
+        <v>-6.098721069400916</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.402928074643327</v>
+        <v>-6.431556719726679</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.080286548099927</v>
+        <v>-5.103108993795679</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.957657516765302</v>
+        <v>-2.969874996303332</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.844036834260343</v>
+        <v>-3.857734235606422</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5599967942938804</v>
+        <v>0.5637948806603248</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.67361402102415</v>
+        <v>4.688543208727332</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.897065925114674</v>
+        <v>3.907645929252908</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.408998447035323</v>
+        <v>4.420062873871423</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.542332957153818</v>
+        <v>6.558334247222639</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.221454284182464</v>
+        <v>7.240877215208045</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.938247284467522</v>
+        <v>2.946003357993547</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.471063885686021</v>
+        <v>2.478047007038697</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.8833464422518063</v>
+        <v>0.8846817023802274</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.941618203788586</v>
+        <v>1.947694433927261</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5532114564069346</v>
+        <v>-0.5571529224512801</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1371489097483547</v>
+        <v>-0.1393692296174507</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.703379473943976</v>
+        <v>-1.709153500748698</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8577287684101265</v>
+        <v>-0.8589968618690449</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>244</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.03442192676739353</v>
+        <v>-0.03486507666719518</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4164873430102958</v>
+        <v>-0.4165347076920511</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8279882126881972</v>
+        <v>0.827623464156197</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.59758560759068</v>
+        <v>2.596343735322925</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.288672589239916</v>
+        <v>3.287266762304441</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5122461287821238</v>
+        <v>-0.5116237757559716</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.091544744109434</v>
+        <v>3.089798458222496</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.9850170830329503</v>
+        <v>0.984444253762355</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.534999196591976</v>
+        <v>-1.533795378000015</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.975288316046189</v>
+        <v>-1.974172074885793</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.770205574789856</v>
+        <v>-1.768617171175435</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9161502862969684</v>
+        <v>-0.915197999803965</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.977763192902081</v>
+        <v>-2.975749159537003</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.367802223186743</v>
+        <v>-4.365372089555706</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-6.678460346641643</v>
+        <v>-6.704193936275225</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.52791942216102</v>
+        <v>-6.5545694552981</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.19591588206157</v>
+        <v>-1.201854771833474</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.946720018176542</v>
+        <v>-1.956557391438366</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.360673744724863</v>
+        <v>2.368193619493617</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.217587048079288</v>
+        <v>2.224519151491066</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8112674277233083</v>
+        <v>0.815619334831446</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.427784469470446</v>
+        <v>3.443330422094874</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.485727314565679</v>
+        <v>2.493562666613734</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.448098310990844</v>
+        <v>-1.454996827467902</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5497915364977004</v>
+        <v>0.5469210531157884</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.905760596926783</v>
+        <v>1.910371603245274</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.0235215958847661</v>
+        <v>-0.02710560810791662</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.861298364778243</v>
+        <v>-2.874729408575092</v>
       </c>
     </row>
     <row r="16">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 10.08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4087~4100</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4087</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2007553933807031</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 14.17</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3955~3968</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3955</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2504947718228721</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 18.25</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3715~3728</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3715</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2133954017550366</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 22.34</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3391~3404</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3391</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.4370340898926983</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 26.43</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3106~3115</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3106</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2301959446080488</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 30.51</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2798~2802</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2798</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.5305546656774993</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 34.6</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2481~2485</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2481</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.8636596481777872</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 38.68</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2129~2131</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2129</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.5929221306276204</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 42.77</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1868~1869</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1868</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.7545405138964441</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 46.86</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1624~1625</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1624</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.8626690894407432</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 50.94</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1398~1398</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1398</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.08166897592735722</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 55.03</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1207~1207</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1207</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.1163379846781822</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 59.12</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1041~1041</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1041</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.05219088247974923</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 63.2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>918~918</t>
-        </is>
+      <c r="B19" t="n">
+        <v>918</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.09692415898993545</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 67.29</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>767~767</t>
-        </is>
+      <c r="B20" t="n">
+        <v>767</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.570446947065129</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 71.37</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>648~648</t>
-        </is>
+      <c r="B21" t="n">
+        <v>648</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.1300184699134803</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 75.46</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>558~558</t>
-        </is>
+      <c r="B22" t="n">
+        <v>558</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.342900685801375</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 79.55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>496~496</t>
-        </is>
+      <c r="B23" t="n">
+        <v>496</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.6789221911777119</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 83.63</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>439~439</t>
-        </is>
+      <c r="B24" t="n">
+        <v>439</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.696171805403594</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 87.72</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>384~384</t>
-        </is>
+      <c r="B25" t="n">
+        <v>384</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.712188320209975</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 91.8</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>333~333</t>
-        </is>
+      <c r="B26" t="n">
+        <v>333</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-2.643588470360129</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 95.89</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>277~277</t>
-        </is>
+      <c r="B27" t="n">
+        <v>277</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-3.03495456569734</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 99.98</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>231~231</t>
-        </is>
+      <c r="B28" t="n">
+        <v>231</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-2.709888536660188</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 104.1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>191~191</t>
-        </is>
+      <c r="B29" t="n">
+        <v>191</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-4.32589905319427</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 108.1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>167~167</t>
-        </is>
+      <c r="B30" t="n">
+        <v>167</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-5.78685149386267</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 112.2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B31" t="n">
+        <v>141</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-4.266487965600049</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 116.3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B32" t="n">
+        <v>124</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-3.299889933113199</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 120.4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>108~108</t>
-        </is>
+      <c r="B33" t="n">
+        <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-6.197142023913678</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 124.5</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>101~101</t>
-        </is>
+      <c r="B34" t="n">
+        <v>101</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-6.948883864764426</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 128.6</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-8.445819272590931</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 10.08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>9.41132358455193</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 14.17</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>216~216</t>
-        </is>
+      <c r="B7" t="n">
+        <v>216</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4.451006124234468</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 18.25</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>456~456</t>
-        </is>
+      <c r="B8" t="n">
+        <v>456</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.673228346456689</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 22.34</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>780~780</t>
-        </is>
+      <c r="B9" t="n">
+        <v>780</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1.865536038764382</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 26.43</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1065~1069</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1065</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.640331558181046</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 30.51</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1373~1382</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1373</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1.052147786881193</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 34.6</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1690~1699</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1690</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.244054322521045</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 38.68</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2042~2053</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2042</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.599596263326319</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 42.77</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2303~2315</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2303</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.5951145955567654</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 46.86</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2547~2559</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2547</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.535088448058886</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 50.94</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2773~2786</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2773</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.05266301511306892</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 55.03</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2964~2977</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2964</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.05810073203396371</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 59.12</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3130~3143</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3130</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.02764131098312106</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 63.2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3253~3266</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3253</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.01727815253956777</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 67.29</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3404~3417</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3404</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.137570599987562</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 71.37</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3523~3536</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3523</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.03303108039096969</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 75.46</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3613~3626</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3613</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.04379278844970003</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 79.55</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3675~3688</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3675</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.08248358868372918</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 83.63</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3732~3745</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3732</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.1901397839288776</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 87.72</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3787~3800</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3787</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.1644564166321274</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 91.8</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3838~3851</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3838</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.2201425678710365</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 95.89</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3894~3907</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3894</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.2068432257332091</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 99.98</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3940~3953</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3940</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.1501235315481821</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 104.1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3980~3993</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3980</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1987730496873468</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 108.1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4004~4017</t>
-        </is>
+      <c r="B30" t="n">
+        <v>4004</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.2324765416272143</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 112.2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4030~4043</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4030</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.1407442175095426</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 116.3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4047~4060</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4047</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.09276857634174718</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 120.4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4063~4076</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4063</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1562182057959092</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 124.5</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4070~4083</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4070</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1639214642622235</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 128.6</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4087~4100</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4087</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1650982651558834</v>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_7.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>132</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.289541892519004</v>
+        <v>1.302023651315309</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.991673730231902</v>
+        <v>8.004549880311657</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.577996744590031</v>
+        <v>4.590970365877574</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.97602946073993</v>
+        <v>6.988979766735213</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.44054077607592</v>
+        <v>6.453625049800358</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.226895130953004</v>
+        <v>5.239913990333164</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.899878930111534</v>
+        <v>5.912924424921563</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.434928241053044</v>
+        <v>5.448091106857426</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.13199745696145</v>
+        <v>6.145181301914874</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.797942898784129</v>
+        <v>6.811336080234732</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.623133455878175</v>
+        <v>9.636582296048047</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.17438926538392</v>
+        <v>11.1878361240982</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.51453139185873</v>
+        <v>11.52808472242367</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.76726576439393</v>
+        <v>11.75683612869542</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>240</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.8247621043310929</v>
+        <v>-0.812286241381976</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3550332385381054</v>
+        <v>-0.3421670204552498</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.913300448053235</v>
+        <v>0.9262681632772995</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.276450733369785</v>
+        <v>7.289398860590339</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.98831471320198</v>
+        <v>8.001397748526671</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.624301291790978</v>
+        <v>6.637318853441855</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.293874612996589</v>
+        <v>5.306918018410776</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.908958295621041</v>
+        <v>6.922120219269438</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.433808949206025</v>
+        <v>6.446991632707288</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.002624116471857</v>
+        <v>6.016016066806394</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.134385048386967</v>
+        <v>4.147832054582246</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.504230303441688</v>
+        <v>2.517675520568396</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.00217705123366585</v>
+        <v>0.01572935746414572</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.6687809159085418</v>
+        <v>0.6583512802103897</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>324</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.12721815217953</v>
+        <v>2.139689550527592</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.597027131889114</v>
+        <v>3.609890236990289</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.204670502037999</v>
+        <v>3.21763403916313</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.795362884627139</v>
+        <v>1.808302125348213</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.029395748730259</v>
+        <v>4.042472082449031</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.635741804643949</v>
+        <v>4.648754522179722</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.092900558919879</v>
+        <v>6.105941185992691</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.936485644193048</v>
+        <v>5.949644473704851</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.569333635873029</v>
+        <v>5.58251373547936</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.263487804043891</v>
+        <v>6.276878002312344</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.369416829400805</v>
+        <v>6.382862899036766</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.097498861138035</v>
+        <v>6.110943613348752</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.753826314532347</v>
+        <v>4.767378422628376</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.079274743069362</v>
+        <v>4.068845107371075</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>285</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.691206999556336</v>
+        <v>-2.861367150083787</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.780742464056551</v>
+        <v>-3.955395935571786</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.640919995454134</v>
+        <v>-3.817102771910875</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.209034421692806</v>
+        <v>-4.19598847302327</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.799905170294274</v>
+        <v>-5.786722763113865</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.264589587026336</v>
+        <v>-4.438887781469894</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.151840669675664</v>
+        <v>-7.138753286086747</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.782076430209933</v>
+        <v>-7.958659361869387</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.794065012613125</v>
+        <v>-6.780894350416638</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.841494597715936</v>
+        <v>-4.828111380620825</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.500852256034158</v>
+        <v>-7.487412282069769</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.169633750395953</v>
+        <v>-8.156193166952434</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.487193156413639</v>
+        <v>-6.473642880176534</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.133850663038643</v>
+        <v>-4.144280298736703</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>308</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.498387501990393</v>
+        <v>2.511884982318932</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.051499380213365</v>
+        <v>-2.039157886276321</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.453012149705955</v>
+        <v>-2.440736336881336</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.789335883735667</v>
+        <v>-2.950414664595158</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.778332930493157</v>
+        <v>-4.941186979470288</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.829268300372576</v>
+        <v>-3.817203305702066</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.09329264799657</v>
+        <v>-3.255205382334225</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.535223916704062</v>
+        <v>-4.523311698655462</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.393124779436206</v>
+        <v>-5.556928909911719</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.44588811266334</v>
+        <v>-4.610930374164148</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.678286884308136</v>
+        <v>-3.664849538184072</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.022531649411398</v>
+        <v>-2.009092293938927</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.793831281550965</v>
+        <v>-1.780281752556157</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.193773196645452</v>
+        <v>-2.204202832343604</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.076490954458905</v>
+        <v>1.946486046036803</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.4769443316324242</v>
+        <v>-0.6106819574019866</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.760706592023631</v>
+        <v>-2.901293258765783</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.670566762892484</v>
+        <v>-7.828938171827751</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.152917734107767</v>
+        <v>-9.314760073642013</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.651632607880615</v>
+        <v>-6.805472316589267</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.95668347479878</v>
+        <v>-3.097081607490047</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.53324991727218</v>
+        <v>-1.667018302715249</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.224091626137778</v>
+        <v>-2.360105013124148</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.073527450160107</v>
+        <v>-3.209506996672786</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.854026032835037</v>
+        <v>-4.994146531659815</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.082131189388811</v>
+        <v>-6.226299905993883</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.2969428919438</v>
+        <v>-4.434076043016091</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.524962512061755</v>
+        <v>-1.678146610084774</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.501160144951392</v>
+        <v>-2.347905240082525</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.704098775374064</v>
+        <v>-2.554816125945777</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.102780728756557</v>
+        <v>-2.953765950288549</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.391649007351688</v>
+        <v>-4.239306722767218</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.636638500313552</v>
+        <v>-6.480484892751598</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.321962629156403</v>
+        <v>-8.160795784043231</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.418591734370011</v>
+        <v>-6.26197140695983</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.468560345341828</v>
+        <v>-5.315363354473497</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.813956500782474</v>
+        <v>-5.660125460147761</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-6.098721069400916</v>
+        <v>-5.946244953803458</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.431556719726679</v>
+        <v>-6.43723312496784</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.103108993795679</v>
+        <v>-5.112070691969095</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.969874996303332</v>
+        <v>-2.825202666037455</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.857734235606422</v>
+        <v>-3.733763922811143</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5637948806603248</v>
+        <v>0.5719022199112018</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.688543208727332</v>
+        <v>4.684099114987035</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.907645929252908</v>
+        <v>3.908354711118463</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.420062873871423</v>
+        <v>4.420180566780154</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.558334247222639</v>
+        <v>6.55284492101358</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.240877215208045</v>
+        <v>7.231342616072496</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.946003357993547</v>
+        <v>2.950053840454103</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.478047007038697</v>
+        <v>2.483110735259345</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.8846817023802274</v>
+        <v>0.8963283156845989</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.947694433927261</v>
+        <v>1.954036463945421</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5571529224512801</v>
+        <v>-0.5391140117086906</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1393692296174507</v>
+        <v>-0.1233360090271205</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.709153500748698</v>
+        <v>-1.687962598221375</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.6997912134280924</v>
       </c>
     </row>
     <row r="14">
@@ -988,101 +988,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.03486507666719518</v>
+        <v>0.193405443473246</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4165347076920511</v>
+        <v>-0.1828203182977148</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.827623464156197</v>
+        <v>1.068177494270167</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.596343735322925</v>
+        <v>2.843612439539413</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.287266762304441</v>
+        <v>3.53972382209453</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5116237757559716</v>
+        <v>-0.2760911806025348</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.089798458222496</v>
+        <v>3.340525646401076</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.984444253762355</v>
+        <v>1.228543351567595</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.533795378000015</v>
+        <v>-1.299792828712356</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.974172074885793</v>
+        <v>-1.738277552118142</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.768617171175435</v>
+        <v>-1.530985241811869</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.915197999803965</v>
+        <v>-0.6741996223720932</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.975749159537003</v>
+        <v>-2.739395749236429</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.365372089555706</v>
+        <v>-4.161607567526055</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 48.9</t>
+          <t>X ≈ 48.89</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-6.704193936275225</v>
+        <v>-6.893246497451337</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.5545694552981</v>
+        <v>-6.75098774329139</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.201854771833474</v>
+        <v>-1.423492654280324</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.956557391438366</v>
+        <v>-2.174324779414427</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.368193619493617</v>
+        <v>2.12913672817222</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.224519151491066</v>
+        <v>1.987336762543137</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.815619334831446</v>
+        <v>0.5842916340262363</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.443330422094874</v>
+        <v>3.198485080393368</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.493562666613734</v>
+        <v>2.252652665676401</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.454996827467902</v>
+        <v>-1.682050282459656</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5469210531157884</v>
+        <v>0.3102022468786316</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.910371603245274</v>
+        <v>1.667791869234073</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.02710560810791662</v>
+        <v>-0.5158281606212398</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.874729408575092</v>
+        <v>-3.121017295413502</v>
       </c>
     </row>
     <row r="16">
@@ -1095,98 +1095,98 @@
         <v>191</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.137417377801718</v>
+        <v>-0.1248950881260953</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.963050894050895</v>
+        <v>2.975960703626946</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.662423025150645</v>
+        <v>4.675430156568247</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.316236367182221</v>
+        <v>5.329215509580685</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.636453895565495</v>
+        <v>1.649564699940434</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.981016252129386</v>
+        <v>2.994059148423752</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.896282534857107</v>
+        <v>2.909348789157583</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.429099136075543</v>
+        <v>2.442280145370781</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.891659459317388</v>
+        <v>2.904858198272152</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.135775111985794</v>
+        <v>4.149180239638625</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.025262625364554</v>
+        <v>6.038719919074772</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.488965154437793</v>
+        <v>4.502417443157903</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.16295138118916</v>
+        <v>6.176507427540763</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.794871666345031</v>
+        <v>3.784442030646879</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 57.08</t>
+          <t>X ≈ 57.07</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>166</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5186098725611785</v>
+        <v>0.5311321622368013</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.919084452367933</v>
+        <v>1.931994261943984</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.283013169891241</v>
+        <v>-0.2700060384736389</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.176856422825971</v>
+        <v>-6.163877280427506</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.116047663306674</v>
+        <v>1.129158467681613</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.015899239576562</v>
+        <v>2.028942135870928</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.135984799412775</v>
+        <v>3.149051053713251</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>6.885668870510735</v>
+        <v>6.898849879805972</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8.02948826143686</v>
+        <v>8.042687000391624</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.769724522192064</v>
+        <v>4.783129649844895</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.76979047498299</v>
+        <v>5.783247768693208</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7.008992909436785</v>
+        <v>7.022445198156895</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10.20319612981711</v>
+        <v>10.21675217616871</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8.043278907876541</v>
+        <v>8.032849272178389</v>
       </c>
     </row>
     <row r="18">
@@ -1199,98 +1199,98 @@
         <v>123</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.165098265155883</v>
+        <v>1.177620554831506</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>6.87059782292333</v>
+        <v>6.883507632499381</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.784672205757488</v>
+        <v>0.7976793371750901</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.353949728609038</v>
+        <v>3.366928871007502</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.628536643618261</v>
+        <v>3.641647447993201</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.178011101659031</v>
+        <v>7.191053997953397</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.280269254305402</v>
+        <v>6.293335508605878</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>6.626093985605344</v>
+        <v>6.639274994900582</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9.817126619748201</v>
+        <v>9.830325358702964</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>14.65805834528933</v>
+        <v>14.67146347294216</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>13.64029689089035</v>
+        <v>13.65375418460057</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>15.30069630839853</v>
+        <v>15.31414859711864</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>13.25442543729103</v>
+        <v>13.26798148364263</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13.5041467695674</v>
+        <v>13.49371713386925</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 65.25</t>
+          <t>X ≈ 65.24</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>151</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.48681580365372</v>
+        <v>-3.474293513978097</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.449382794101389</v>
+        <v>-2.436472984525338</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.493258123214531</v>
+        <v>-5.480250991796929</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-12.6477732025276</v>
+        <v>-12.63479406012913</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-11.86169110634145</v>
+        <v>-11.84858030196651</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.252990890480099</v>
+        <v>-8.239947994185734</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.662227919010689</v>
+        <v>-9.649161664710213</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.831398072759036</v>
+        <v>-4.818217063463798</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.230146303312246</v>
+        <v>-4.216947564357483</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.742523143969265</v>
+        <v>-5.729118016316434</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.622773157028575</v>
+        <v>-4.609315863318358</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.277131721537486</v>
+        <v>-1.263679432817376</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.035134676853168</v>
+        <v>-1.021578630501565</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.109916655835235</v>
+        <v>-2.120346291533387</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>119</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.968746553739649</v>
+        <v>2.981268843415272</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>11.04633784762419</v>
+        <v>11.05934497904179</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.69759938359302</v>
+        <v>13.71057852599149</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.276825227344339</v>
+        <v>7.289936031719279</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.893594896152436</v>
+        <v>5.906637792446801</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.60718050661125</v>
+        <v>1.620246760911726</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.061683564439107</v>
+        <v>-3.04850255514387</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.442011181713895</v>
+        <v>-1.428812442759131</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.292136366741822</v>
+        <v>-2.278731239088991</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.816217422151837</v>
+        <v>-0.8027601284416193</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.46250653371397</v>
+        <v>-2.44905424499386</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3617527412975292</v>
+        <v>-0.3481966949459263</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.398547358641956</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.698859250364528</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>8.117210289047989</v>
+        <v>8.829246191008622</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>7.722341582451399</v>
+        <v>7.310879300635605</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>8.963705826170077</v>
+        <v>9.688295455459858</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>8.42528461109778</v>
+        <v>9.150005902364164</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.500504326591219</v>
+        <v>7.200188920763296</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.97132616487449</v>
+        <v>1.497501033407246</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.615253877204104</v>
+        <v>2.154027895238421</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.887587324355202</v>
+        <v>5.463832255569642</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.037462139327275</v>
+        <v>4.613913459239782</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>7.05493103723191</v>
+        <v>6.656403312215474</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.978203083466234</v>
+        <v>5.567185958952884</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.446837361410225</v>
+        <v>4.023439600021504</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.807669804797619</v>
+        <v>5.372770755866007</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.345271357209285</v>
+        <v>1.487337937719523</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.346600970051583</v>
+        <v>1.463453431957291</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.886977413964374</v>
+        <v>-2.105921127400926</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.307791847675304</v>
+        <v>4.373510365393876</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>6.382273858409761</v>
+        <v>5.422522399599764</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2281028928996207</v>
+        <v>-0.6293099199714973</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.982078853046694</v>
+        <v>5.635186069968682</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.740701905878005</v>
+        <v>8.342720600785114</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>9.292605245502152</v>
+        <v>9.869040031563927</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.829576834667776</v>
+        <v>7.431819647932478</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.399017058737293</v>
+        <v>4.052515315069201</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.820496990276276</v>
+        <v>2.499591880122857</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.825564072281537</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.188745965811748</v>
+        <v>-2.456728084868836</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>57</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.155684486807665</v>
+        <v>7.168206776483288</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.473432985805815</v>
+        <v>-1.460523176229763</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.377073622226966</v>
+        <v>-5.364066490809364</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-7.001206454531747</v>
+        <v>-6.988227312133283</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.276469774867117</v>
+        <v>-2.263358970492177</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-8.996571696800537</v>
+        <v>-8.983528800506171</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.326919449160584</v>
+        <v>-7.313853194860108</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-7.794102847942035</v>
+        <v>-7.780921838646798</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.346330804299768</v>
+        <v>-4.333132065345005</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.442070024415465</v>
+        <v>-3.428664896762633</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-12.41875317329441</v>
+        <v>-12.40529587958419</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-14.1387559808613</v>
+        <v>-14.12530369214119</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-11.05023866198164</v>
+        <v>-11.03668261563004</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.537359434968458</v>
+        <v>-5.54778907066661</v>
       </c>
     </row>
     <row r="24">
@@ -1511,98 +1511,98 @@
         <v>55</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.584347411119069</v>
+        <v>-1.571825121443446</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-12.28683011499242</v>
+        <v>-12.27392030541637</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-12.68169882158901</v>
+        <v>-12.66869169017141</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.096900234436049</v>
+        <v>-7.083921092037585</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-9.453503267689982</v>
+        <v>-9.440392463315042</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-12.79242496633802</v>
+        <v>-12.77938207004365</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-12.87715868361024</v>
+        <v>-12.86409242930976</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-15.16252390057361</v>
+        <v>-15.14934289127837</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-18.85988742311955</v>
+        <v>-18.84668868416478</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-16.07364897178379</v>
+        <v>-16.06024384413096</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-12.64203865973779</v>
+        <v>-12.62858136602757</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-8.971291866028665</v>
+        <v>-8.957839577308555</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-11.20972829515538</v>
+        <v>-11.19617224880378</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-12.77818878106091</v>
+        <v>-12.78861841675906</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 89.76</t>
+          <t>X ≈ 89.75</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>51</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.369306777829237</v>
+        <v>4.38182906750486</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.75773316486498</v>
+        <v>2.770642974441031</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.441057110359061</v>
+        <v>-7.428049978941459</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.389235350300581</v>
+        <v>-3.376256207902117</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.006087937921762432</v>
+        <v>0.007022866453176846</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.59099894138258</v>
+        <v>-5.577956045088214</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.10370037116185</v>
+        <v>-8.090519361866612</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.203915943618661</v>
+        <v>-6.190717204663898</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-7.054041128646588</v>
+        <v>-7.040636000993757</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.376441511787689</v>
+        <v>-1.362984218077472</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.263626981893246</v>
+        <v>-5.250174693173136</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-9.605450220289129</v>
+        <v>-9.591894173937526</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-11.31651320173832</v>
+        <v>-11.32694283743648</v>
       </c>
     </row>
     <row r="26">
@@ -1615,98 +1615,98 @@
         <v>56</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7077240344956834</v>
+        <v>-0.6952017448200607</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-14.81929764745995</v>
+        <v>-14.8063878378839</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-11.64273778262791</v>
+        <v>-11.62973065121031</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-16.86962750716332</v>
+        <v>-16.85664836476486</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-13.83662015080687</v>
+        <v>-13.82350934643193</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-11.75346392737692</v>
+        <v>-11.74042103108255</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-15.40962621607778</v>
+        <v>-15.3965599617773</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-17.66252390057361</v>
+        <v>-17.64934289127837</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-15.93780950104163</v>
+        <v>-15.92461076208686</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-16.78793468606951</v>
+        <v>-16.77452955841667</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-16.99268801038708</v>
+        <v>-16.97923071667687</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-16.9583048530417</v>
+        <v>-16.94485256432159</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-12.0214166068438</v>
+        <v>-12.0078605604922</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-15.34312384599603</v>
+        <v>-15.35355348169418</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 97.94</t>
+          <t>X ≈ 97.92</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>46</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.667351363688269</v>
+        <v>-4.654829074012646</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.452838020130756</v>
+        <v>-8.439928210554704</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.021858490663902</v>
+        <v>2.034865622081504</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.84776379718443</v>
+        <v>10.8607429395829</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.96151649515582</v>
+        <v>5.974627299530759</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>10.60678451982787</v>
+        <v>10.61982741612223</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.348137759077389</v>
+        <v>8.361204013377865</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.707041316817701</v>
+        <v>5.720222326112939</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.049610743277618</v>
+        <v>-3.036412004322855</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.725822884827373</v>
+        <v>-1.712417757174542</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2433368343333058</v>
+        <v>0.2567941280435235</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.896193051799472</v>
+        <v>-1.882740763079362</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.49036070622256</v>
+        <v>-4.476804659870957</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.066726330468086</v>
+        <v>-2.077155966166238</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>40</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.006561679790067</v>
+        <v>5.01908396946569</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.000119360229142</v>
+        <v>8.013126491646744</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.630372492836784</v>
+        <v>5.643351635235248</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.591951277764437</v>
+        <v>2.605062082139376</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.88939321548024</v>
+        <v>2.902436111774605</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3046594982078474</v>
+        <v>0.3177257525083235</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.723523786755941</v>
+        <v>-2.710325047801177</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.073648971783882</v>
+        <v>-1.060243844131051</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.721597703898581</v>
+        <v>8.735054997608799</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.755980861244012</v>
+        <v>8.769433149964122</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.335726250299111</v>
+        <v>8.349282296650713</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.0854475825754</v>
+        <v>11.07501794687725</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>4.040823099900429</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>11.12528918074965</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>12.16678602689591</v>
+        <v>10.73051779599466</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>16.46370582616995</v>
+        <v>19.55639511349595</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>20.09195127776451</v>
+        <v>23.36593164735684</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>16.22272654881351</v>
+        <v>19.31547959003539</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.637992831541283</v>
+        <v>6.187290969899728</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.9958572339069462</v>
+        <v>1.372396239156409</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-3.036412004322891</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.906982305117111</v>
+        <v>0.4614952863038368</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-10.44506896276814</v>
+        <v>-8.438858045869459</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-10.41068580542271</v>
+        <v>-8.4044798935142</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-4.476804659871028</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-10.58121908409127</v>
+        <v>-8.598895096601076</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-14.03189985867151</v>
+        <v>-11.74017528979361</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-15.64347347163577</v>
+        <v>-13.35136138285744</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-8.346034485924669</v>
+        <v>-6.338725360205075</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-12.06193519947102</v>
+        <v>-13.61590762402412</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-12.60035641454324</v>
+        <v>-14.15419717711986</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-12.30291447682752</v>
+        <v>-13.85682314748473</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-16.23380204025364</v>
+        <v>-17.6452372104546</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-12.8548315928813</v>
+        <v>-14.40860215053763</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-12.91583147906361</v>
+        <v>-14.46958430706041</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-13.76595666409153</v>
+        <v>-15.31950310339027</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-13.97070998840906</v>
+        <v>-15.52420426165046</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-21.62863452337132</v>
+        <v>-22.89723351670249</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-22.04888913431628</v>
+        <v>-23.31738437001596</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-17.95301395588614</v>
+        <v>-19.38794501608567</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>17</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-11.31696773197469</v>
+        <v>-11.30444544229906</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-12.92854134493886</v>
+        <v>-12.91563153536281</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.558704169182505</v>
+        <v>-1.545697037764903</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.33625484577785</v>
+        <v>10.34923398817632</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.797833630705853</v>
+        <v>9.810944435080792</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.09527556842134</v>
+        <v>10.10831846471571</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15.89289479232546</v>
+        <v>15.90596104662593</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.221347429985293</v>
+        <v>-2.208166420690056</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.36471150736165</v>
+        <v>15.37791024631642</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.632233381157249</v>
+        <v>8.64563850881008</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.427480056839755</v>
+        <v>8.440937350549973</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.5795102730088</v>
+        <v>2.59296256172891</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.72309727911265</v>
+        <v>-3.709541232761048</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.473375946836363</v>
+        <v>-3.483805582534515</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>16</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>16.25656167979002</v>
+        <v>16.26908396946565</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.64498806682568</v>
+        <v>14.65789787640173</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.000119360229093</v>
+        <v>8.013126491646695</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.908048722235534</v>
+        <v>-4.894937917860595</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.86060678451979</v>
+        <v>-10.84756388822542</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-4.695340501792025</v>
+        <v>-4.682274247491549</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.162523900573696</v>
+        <v>-5.149342891278458</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.52647621324417</v>
+        <v>13.53967495219894</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1763510282162457</v>
+        <v>0.1897561558690768</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>6.235054997608799</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.255980861243927</v>
+        <v>6.269433149964037</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.08572625029911</v>
+        <v>12.09928229665071</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.3354475825754</v>
+        <v>12.32501794687725</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>7</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.649418822647064</v>
+        <v>4.661941112322687</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-25.53358336174566</v>
+        <v>-25.52067355216961</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.51248465002047</v>
+        <v>-11.499505507622</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-12.05090586509264</v>
+        <v>-12.0377950607177</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-11.75346392737698</v>
+        <v>-11.74042103108261</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-26.12391193036354</v>
+        <v>-26.11084567606306</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-12.30538104343086</v>
+        <v>-12.29220003413562</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-12.36638092961316</v>
+        <v>-12.35318219065839</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.069208171073399</v>
+        <v>1.08261329872623</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-27.70697372467285</v>
+        <v>-27.69351643096263</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-13.38687628161323</v>
+        <v>-13.37342399289312</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-13.80713089255813</v>
+        <v>-13.79357484620653</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.55740956028185</v>
+        <v>-13.56783919598</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>17</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.447738150378342</v>
+        <v>0.4602604400539647</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>21.97070759552329</v>
+        <v>21.9837147269409</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>16.21860778695433</v>
+        <v>16.23158692935279</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.915480689529169</v>
+        <v>3.928591493904108</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.669430313931642</v>
+        <v>-1.656387417637276</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.754164031203828</v>
+        <v>-1.741097776903352</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.1037003711618</v>
+        <v>-8.090519361866562</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-19.92940613969705</v>
+        <v>-19.91620740074229</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-9.014825442372114</v>
+        <v>-9.001420314719283</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>2.558584409373509</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.579510273008765</v>
+        <v>2.592962561728875</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-9.605450220289079</v>
+        <v>-9.591894173937476</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-9.355728888012791</v>
+        <v>-9.366158523710943</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2007553933807031</v>
+        <v>-0.2009843065645853</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.09183798830962786</v>
+        <v>-0.09210212359818115</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.107494109756189</v>
+        <v>-0.1077566505830276</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1348215515860716</v>
+        <v>-0.1350768664730069</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1717205972354918</v>
+        <v>-0.1719698924761204</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2027923767054247</v>
+        <v>-0.2030326382254657</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2253844685727628</v>
+        <v>-0.2256197908371789</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2394845651228366</v>
+        <v>-0.2397190515128642</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.287062398681627</v>
+        <v>-0.2872857123503749</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3171102282003702</v>
+        <v>-0.3173308431534991</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3370820027028856</v>
+        <v>-0.337298950081248</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3623854874965105</v>
+        <v>-0.3625961898891745</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4020428299357235</v>
+        <v>-0.4022461944228937</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4077014264776935</v>
+        <v>-0.4073695286609222</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3955</v>
+        <v>3956</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2504947718228721</v>
+        <v>-0.25113522932498</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3616290241749809</v>
+        <v>-0.3622634139207577</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2638745883336071</v>
+        <v>-0.2645392507278146</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.372149575259165</v>
+        <v>-0.3727855306751025</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3924079553333755</v>
+        <v>-0.3930463667886741</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.384010771398458</v>
+        <v>-0.3846476420095186</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4298180383897829</v>
+        <v>-0.430444825336707</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4288707826740961</v>
+        <v>-0.4295044258568694</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5013015645336836</v>
+        <v>-0.5019180798637635</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5545784994423357</v>
+        <v>-0.5551933390805033</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6695089156062224</v>
+        <v>-0.6700978187589683</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.7474308142677373</v>
+        <v>-0.7479998970293025</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.7997641440386047</v>
+        <v>-0.8003259924571964</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.8140467284233353</v>
+        <v>-0.8132530339114368</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3715</v>
+        <v>3716</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2133954017550366</v>
+        <v>-0.2148929680511174</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3620551314570335</v>
+        <v>-0.3635613510659965</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3399235812630437</v>
+        <v>-0.3414482333330966</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.8662718024653344</v>
+        <v>-0.8676521221454223</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9338274547811451</v>
+        <v>-0.9352063742363939</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.8367684820755628</v>
+        <v>-0.8381653919848588</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7995855313461107</v>
+        <v>-0.8009957086788546</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.902916268216714</v>
+        <v>-0.9043133372751484</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.949330238368816</v>
+        <v>-0.9507174154442524</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.9781932041043575</v>
+        <v>-0.9795986828406882</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.9798546898615044</v>
+        <v>-0.9812665942169616</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9574977505396873</v>
+        <v>-0.9589154245382971</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8515719197762408</v>
+        <v>-0.8530313971884027</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.9098417848539384</v>
+        <v>-0.908297446018338</v>
       </c>
     </row>
     <row r="9">
@@ -2370,101 +2370,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4370340898926983</v>
+        <v>-0.4398000246606415</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7403337080787225</v>
+        <v>-0.7431009485100546</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6785990407114468</v>
+        <v>-0.6814077428521941</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.120583108457062</v>
+        <v>-1.123256242483848</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.408048722235492</v>
+        <v>-1.410668585311299</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.359650620942311</v>
+        <v>-1.362269770578408</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.458142149820361</v>
+        <v>-1.460738501684041</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.556400850823835</v>
+        <v>-1.558995628182437</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.572169252009147</v>
+        <v>-1.574764258869735</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.670114362063664</v>
+        <v>-1.672729120927244</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.682055802288808</v>
+        <v>-1.68467990666219</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.631581767697924</v>
+        <v>-1.634220356223267</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.387151108191453</v>
+        <v>-1.3898865804492</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.38653708271508</v>
+        <v>-1.383708468217094</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 26.43</t>
+          <t>X &gt; 26.42</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2301959446080488</v>
+        <v>-0.2176736549324261</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4613522220987889</v>
+        <v>-0.4484424125227378</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.406782726448192</v>
+        <v>-0.3937755950305899</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.8371933388910051</v>
+        <v>-0.8413995686171845</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.005061250343431</v>
+        <v>-1.009260332761009</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.093099556765253</v>
+        <v>-1.080056660470888</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9357003989643431</v>
+        <v>-0.9399035439901908</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9851460085427561</v>
+        <v>-0.9719649992475183</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.093019125875173</v>
+        <v>-1.097214507955393</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.379115209725967</v>
+        <v>-1.383291095818571</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.148135329231039</v>
+        <v>-1.15240480946516</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.031663926400775</v>
+        <v>-1.035970516809755</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.9191820213455699</v>
+        <v>-0.9235619761935538</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.134449391024084</v>
+        <v>-1.130485754442361</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.5305546656774993</v>
+        <v>-0.5180323760018766</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2863110052655955</v>
+        <v>-0.2734011956895444</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1815365997993794</v>
+        <v>-0.1685294683817773</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6223041666922384</v>
+        <v>-0.6093250242937742</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.589704682264049</v>
+        <v>-0.5765938778891098</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.7919058566111943</v>
+        <v>-0.7788629603168289</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6981956052896052</v>
+        <v>-0.6851293509891292</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5943583045707541</v>
+        <v>-0.5811772952755163</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.6196693970342864</v>
+        <v>-0.6064706580795232</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.041529057436939</v>
+        <v>-1.028123929784108</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8696197184505792</v>
+        <v>-0.8759371508565792</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.9225905673274113</v>
+        <v>-0.9288888778830682</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.8229018311585534</v>
+        <v>-0.8292891319207172</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.017840480326669</v>
+        <v>-1.012334679060594</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8636596481777872</v>
+        <v>-0.8316803105021719</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2619535830736268</v>
+        <v>-0.2304770230350357</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1480066841728416</v>
+        <v>0.1792568214939223</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2782598167803414</v>
+        <v>0.3094819650822842</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5044261268590802</v>
+        <v>0.5354723798063787</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.04320235796048166</v>
+        <v>-0.01188408130672514</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4096262160778252</v>
+        <v>-0.3781712708222926</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4743951279377967</v>
+        <v>-0.4429872999670366</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4146706680436338</v>
+        <v>-0.38329367209721</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.781898468765732</v>
+        <v>-0.7505093308566728</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3605278999661508</v>
+        <v>-0.351831567153873</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2633505926424107</v>
+        <v>-0.2547117192511621</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3790199221424686</v>
+        <v>-0.3705244666343148</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9530449607538998</v>
+        <v>-0.9275998541698698</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5929221306276204</v>
+        <v>-0.5803998409519977</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.141820539843124</v>
+        <v>0.1547303494191752</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6854783466205419</v>
+        <v>0.698485478038144</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.050363107571549</v>
+        <v>1.063342249970013</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.68510003421688</v>
+        <v>1.69821083859182</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.325573412570733</v>
+        <v>1.338616308865099</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5838711359366542</v>
+        <v>0.5969373902371302</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3513193654986608</v>
+        <v>0.3645003747938986</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4780247819911594</v>
+        <v>0.4912235209459226</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.09716285365022514</v>
+        <v>0.1105679813030562</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6432307400318464</v>
+        <v>0.6566880337420642</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5368349203711844</v>
+        <v>0.5502872090912945</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.04934127377328679</v>
+        <v>0.03628370444048556</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4727957241413705</v>
+        <v>-0.4625407385687623</v>
       </c>
     </row>
     <row r="14">
@@ -2633,98 +2633,98 @@
         <v>1868</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7545405138964441</v>
+        <v>-0.7420182242208213</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4934549508307313</v>
+        <v>-0.4805451412546802</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2352718481906564</v>
+        <v>0.2482789796082585</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5795431723444295</v>
+        <v>0.5925223147428937</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.004203819230533</v>
+        <v>1.017314623605472</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.49907753864764</v>
+        <v>0.5121204349420054</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.253830177715642</v>
+        <v>0.266896432016118</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05416951836699724</v>
+        <v>0.06735052766223504</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4212060152772636</v>
+        <v>0.4344047542320268</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.161396430317815</v>
+        <v>-0.1479913026649839</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8109502988691588</v>
+        <v>0.8244075925793766</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6313152646683022</v>
+        <v>0.6447675533884123</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.2950410254597102</v>
+        <v>0.2781212479615718</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.4188350726708521</v>
+        <v>-0.4292647083690042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 46.86</t>
+          <t>X &gt; 46.85</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8626690894407432</v>
+        <v>-0.8819000403744539</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5050119331742309</v>
+        <v>-0.5250664532414788</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1462732063830217</v>
+        <v>0.1256726171080373</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2765263389905215</v>
+        <v>0.2558977606963992</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6611820469952789</v>
+        <v>0.6401174326929535</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6509316770186331</v>
+        <v>0.6299883872972885</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1722635787151887</v>
+        <v>-0.1927293520426829</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.08560082365053034</v>
+        <v>-0.1062924607740712</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7149377517056266</v>
+        <v>0.6937339927892552</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1109664128315515</v>
+        <v>0.08981765648400142</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.19852078082166</v>
+        <v>1.176629413352956</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.863673168936316</v>
+        <v>0.8420038756713808</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7864651665552742</v>
+        <v>0.7293560973887239</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.174117533314309</v>
+        <v>0.1288641007233977</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1398</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.08166897592735722</v>
+        <v>0.09419126560297997</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.472956593292146</v>
+        <v>0.4858664028681972</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3642109195997065</v>
+        <v>0.3772180510173087</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.637525568659278</v>
+        <v>0.6505047110577422</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.385227386491259</v>
+        <v>0.3983381908661983</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3965462913027693</v>
+        <v>0.4095891875971347</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3319642500038427</v>
+        <v>-0.3188979957033666</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6560861323332645</v>
+        <v>-0.6429051230380267</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4274061131010285</v>
+        <v>0.4406048520557917</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3641192685595058</v>
+        <v>0.3775243962123369</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.303858075858528</v>
+        <v>1.317315369568746</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6944644091696262</v>
+        <v>0.7079166978897362</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9179866222590576</v>
+        <v>0.9315426686106605</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6669926469530765</v>
+        <v>0.6565630112549243</v>
       </c>
     </row>
     <row r="17">
@@ -2789,98 +2789,98 @@
         <v>1207</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1163379846781822</v>
+        <v>0.128860274353805</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.07891515878931443</v>
+        <v>0.09182496836536558</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3159535478072755</v>
+        <v>-0.3029464163896733</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.102850373774757</v>
+        <v>-0.08987123137629283</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1872288254032881</v>
+        <v>0.2003396297782274</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.01242948543118416</v>
+        <v>0.0006134108631812296</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8428135755286448</v>
+        <v>-0.8297473212281687</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.144296891460101</v>
+        <v>-1.131115882164863</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.03745384373290506</v>
+        <v>0.05065258268766826</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.232721051319885</v>
+        <v>-0.2193159236670539</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5567261214627877</v>
+        <v>0.5701834151730054</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.09400903025809981</v>
+        <v>0.1074613189782099</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.08800462643829832</v>
+        <v>0.1015606727899012</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1720258758645485</v>
+        <v>0.1615962401663964</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 59.12</t>
+          <t>X &gt; 59.11</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1041</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.05219088247974923</v>
+        <v>0.06471317215537198</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2145220196295625</v>
+        <v>-0.2016122100535114</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.3212062881858131</v>
+        <v>-0.308199156768211</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8657231172362927</v>
+        <v>0.8787022596347569</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.03911746412378392</v>
+        <v>0.0522282684987232</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3358709535880351</v>
+        <v>-0.3228280572936697</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.47728094367492</v>
+        <v>-1.464214689374444</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.424771739190319</v>
+        <v>-2.411590729895082</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.236972393864463</v>
+        <v>-1.223773654909699</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.030421306077791</v>
+        <v>-1.01701617842496</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2745598369275513</v>
+        <v>-0.2611025432173335</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.008668514356373</v>
+        <v>-0.9952162256362627</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.524984604648047</v>
+        <v>-1.511428558296444</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.0831403136782</v>
+        <v>-1.093569949376352</v>
       </c>
     </row>
     <row r="19">
@@ -2893,98 +2893,98 @@
         <v>918</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.09692415898993545</v>
+        <v>-0.08440186931431271</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.163835462585993</v>
+        <v>-1.150925653009942</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4693795504461988</v>
+        <v>-0.4563724190285967</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.532333277150407</v>
+        <v>0.5453124195488712</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.441817785416319</v>
+        <v>-0.4287069810413797</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.342632928310678</v>
+        <v>-1.329590032016313</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.516691264319348</v>
+        <v>-2.503625010018872</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.637469434342677</v>
+        <v>-3.624288425047439</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.718077163662237</v>
+        <v>-2.704878424707474</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-3.119067373542769</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.13896874490316</v>
+        <v>-2.125511451192942</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.19391020629412</v>
+        <v>-3.18045791757401</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.505232355365372</v>
+        <v>-3.491676309013769</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.037646099341821</v>
+        <v>-3.048075735039973</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 67.29</t>
+          <t>X &gt; 67.28</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>767</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.570446947065129</v>
+        <v>0.5829692367407517</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.91074856941934</v>
+        <v>-0.8978387598432889</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5196760747011524</v>
+        <v>0.5326832061187545</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.127113040424689</v>
+        <v>3.140092182823153</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.806423246473763</v>
+        <v>1.819534050848702</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.01781564051276519</v>
+        <v>0.03085853680713058</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.109942848597846</v>
+        <v>-1.09687659429737</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.402419598096429</v>
+        <v>-3.389238588801192</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.420394712440398</v>
+        <v>-2.407195973485635</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.618629415069371</v>
+        <v>-2.60522428741654</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.649979871068822</v>
+        <v>-1.636522577358605</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.571268160920262</v>
+        <v>-3.557815872200152</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.991522771865164</v>
+        <v>-3.977966725513561</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.22028905366971</v>
+        <v>-3.230718689367862</v>
       </c>
     </row>
     <row r="21">
@@ -2997,150 +2997,150 @@
         <v>648</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1300184699134803</v>
+        <v>0.1425407595891031</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.944518106013739</v>
+        <v>-1.931608296437687</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.413460886684398</v>
+        <v>-1.400453755266795</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>1.198907190790699</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8018278209743883</v>
+        <v>0.8149386253493276</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.061224068470445</v>
+        <v>-1.048181172176079</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.608920748705685</v>
+        <v>-1.595854494405209</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.464993036376086</v>
+        <v>-3.451812027080848</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.600066996632457</v>
+        <v>-2.586868257677693</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.678587243388776</v>
+        <v>-2.665182115735945</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.803093654126116</v>
+        <v>-1.789636360415898</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.774883336286855</v>
+        <v>-3.761431047566745</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.658100910194719</v>
+        <v>-4.644544863843116</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.254058590264108</v>
+        <v>-4.264488225962261</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 75.46</t>
+          <t>X &gt; 75.45</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.342900685801375</v>
+        <v>-0.4236709500334612</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.56737752457208</v>
+        <v>-3.644874932184948</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.886977413964374</v>
+        <v>-2.787410180982924</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.0685522383461219</v>
+        <v>-0.1527127654804232</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4277619838842313</v>
+        <v>-0.5121114420108199</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.280857680577171</v>
+        <v>-2.361427931159277</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.186379928315404</v>
+        <v>-2.088356537294857</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.445678022437413</v>
+        <v>-4.344333946734544</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.969043500017563</v>
+        <v>-3.868643473561434</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.923111337375239</v>
+        <v>-3.82410788706482</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.231807314022568</v>
+        <v>-3.134354662498531</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.347961791085737</v>
+        <v>-5.246667028926751</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.126639341098738</v>
+        <v>-6.024599635370755</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.87691800882245</v>
+        <v>-5.798863985144223</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 79.55</t>
+          <t>X &gt; 79.54</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>496</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6789221911777119</v>
+        <v>-0.6663999015020892</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.30662483640004</v>
+        <v>-4.293715026823989</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.886977413964374</v>
+        <v>-2.873970282546772</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7405952490988099</v>
+        <v>-0.7276161067003457</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.279016464170979</v>
+        <v>-1.26590565979604</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.594477752261767</v>
+        <v>-2.581434855967402</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.082437275985662</v>
+        <v>-3.069371021685185</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.968975513476835</v>
+        <v>-5.955794504181597</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.626749593207528</v>
+        <v>-5.613550854252765</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.267197358880615</v>
+        <v>-5.253792231227784</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-4.060660360617547</v>
+        <v>-4.047203066907329</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.212939514198787</v>
+        <v>-6.223369149896939</v>
       </c>
     </row>
     <row r="24">
@@ -3153,98 +3153,98 @@
         <v>439</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.696171805403594</v>
+        <v>-1.683649515727971</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.674488015178788</v>
+        <v>-4.661578205602737</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.563661960955329</v>
+        <v>-2.550654829537727</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.07228593247221227</v>
+        <v>0.08526507487067647</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.149506581005419</v>
+        <v>-1.136395776630479</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.763226374497052</v>
+        <v>-1.750183478202686</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.531331390174792</v>
+        <v>-2.518265135874316</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.731999982578166</v>
+        <v>-5.718818973282929</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5.792999868760468</v>
+        <v>-5.779801129805705</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.504172889779277</v>
+        <v>-5.490767762126445</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.975441020474996</v>
+        <v>-2.961983726764778</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-5.218962191147781</v>
+        <v>-5.205509902427671</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-6.094797667696326</v>
+        <v>-6.081241621344724</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.300657201023682</v>
+        <v>-6.311086836721834</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 87.72</t>
+          <t>X &gt; 87.71</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>384</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.712188320209975</v>
+        <v>-1.699666030534353</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.584178599840897</v>
+        <v>-3.571268790264845</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.114463973104158</v>
+        <v>-1.101456841686556</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.099122492836678</v>
+        <v>1.112101635235142</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.03986794443117248</v>
+        <v>0.05297874880611175</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1835234511864954</v>
+        <v>-0.17048055489213</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.049507168458774</v>
+        <v>-1.036440914158298</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.381273900573611</v>
+        <v>-4.368092891278373</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.921440453422576</v>
+        <v>-3.908241714467813</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.990315638450504</v>
+        <v>-3.976910510797673</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.590902296101419</v>
+        <v>-1.577445002391201</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.681519138755988</v>
+        <v>-4.668066850035878</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.362190416367554</v>
+        <v>-5.348634370015951</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.372885750757938</v>
+        <v>-5.38331538645609</v>
       </c>
     </row>
     <row r="26">
@@ -3257,150 +3257,150 @@
         <v>333</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.643588470360129</v>
+        <v>-2.631066180684506</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.555462383624686</v>
+        <v>-4.542552574048635</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1455262854164729</v>
+        <v>-0.1325191539988708</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.786528648992835</v>
+        <v>1.799507791391299</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.04690623271946492</v>
+        <v>0.0600170370944042</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6446484707354188</v>
+        <v>0.6576913670297841</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.941586748038354</v>
+        <v>-0.9285204937378779</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.811172549222263</v>
+        <v>-3.797991539927025</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.571872135104257</v>
+        <v>-3.558673396149494</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.521096419231284</v>
+        <v>-3.507691291578453</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.623747641446762</v>
+        <v>-1.610290347736544</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.592367487104333</v>
+        <v>-4.578915198384223</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.712321797748942</v>
+        <v>-4.698765751397339</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.462600465472654</v>
+        <v>-4.473030101170806</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 95.89</t>
+          <t>X &gt; 95.88</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>277</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.03495456569734</v>
+        <v>-3.022432276021718</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.480463196712137</v>
+        <v>-2.467553387136086</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.178819721240004</v>
+        <v>2.191826852657606</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.558170326771695</v>
+        <v>5.571149469170159</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.853684129750064</v>
+        <v>2.866794934125004</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.151126067465725</v>
+        <v>3.16416896376009</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.983359859218716</v>
+        <v>1.996426113519192</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.010899351837146</v>
+        <v>-0.9977183425419085</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.071899238019448</v>
+        <v>-1.058700499064685</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.838991932072652</v>
+        <v>-0.8255868044198209</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.483330555884137</v>
+        <v>1.496787849594355</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.092394590019524</v>
+        <v>-2.078942301299413</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.234670861614241</v>
+        <v>-3.221114815262638</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.262927868688138</v>
+        <v>-2.27335750438629</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 99.98</t>
+          <t>X &gt; 99.97</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>231</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.709888536660188</v>
+        <v>-2.697366246984565</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.291159119321421</v>
+        <v>-1.27824930974537</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.210076070185892</v>
+        <v>2.223083201603494</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.504831367295559</v>
+        <v>4.517810509694023</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.666449492536451</v>
+        <v>1.679492388830816</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7159149094633008</v>
+        <v>0.7289811637637769</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.348671086720799</v>
+        <v>-2.335490077425561</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6623935605284288</v>
+        <v>-0.6489884328755977</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.730255712556591</v>
+        <v>1.743713006266809</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.131465026201873</v>
+        <v>-2.118012737481763</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.984620070047207</v>
+        <v>-2.971064023695604</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.301998304870487</v>
+        <v>-2.312427940568639</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>191</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.32589905319427</v>
+        <v>-4.313376763518647</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.796111409614021</v>
+        <v>-2.78320160003797</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.9975015591820622</v>
+        <v>1.010508690599664</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.269115948334054</v>
+        <v>4.282095090732518</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.160014104989635</v>
+        <v>2.173124909364574</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.410335623857129</v>
+        <v>1.423378520151495</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.8020416971607744</v>
+        <v>0.8151079514612505</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.853623377013399</v>
+        <v>-3.840442367718161</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.249701797227118</v>
+        <v>-0.2365030582723548</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5762667728309552</v>
+        <v>-0.5628616451781241</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.266100321699632</v>
+        <v>0.2795576154098498</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.411558405771693</v>
+        <v>-4.398106117051583</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.355373226140678</v>
+        <v>-5.341817179789075</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.10565189386439</v>
+        <v>-5.116081529562543</v>
       </c>
     </row>
     <row r="30">
@@ -3462,49 +3462,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-5.78685149386267</v>
+        <v>-5.457106506724827</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.003215525988608</v>
+        <v>-4.687340218836276</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6076650709085456</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.516600037746862</v>
+        <v>2.190970682854186</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4170307581636408</v>
+        <v>-0.7282712511938882</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7183912156575545</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.3944798574893298</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.264320307759235</v>
+        <v>-4.554104796040278</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.4650989677351021</v>
+        <v>0.1468178093417123</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3850262172928254</v>
+        <v>-0.7031009869881473</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.805430039227929</v>
+        <v>1.473150235704033</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.549408360312867</v>
+        <v>-3.849614469083491</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.167267761676939</v>
+        <v>-5.460241512873097</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.31874403419107</v>
+        <v>-4.639267767408462</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>141</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.266487965600049</v>
+        <v>-4.253965675924427</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.041182145940191</v>
+        <v>-3.02827233636414</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8192682963993931</v>
+        <v>0.8322754278169953</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.20484057794306</v>
+        <v>5.217819720341524</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.829539930246781</v>
+        <v>1.842650734621721</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.41776200980641</v>
+        <v>1.430804906100775</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.460687867002214</v>
+        <v>3.47375412130269</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.680254397027511</v>
+        <v>-2.667073387732273</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.932504582038412</v>
+        <v>2.945703320993175</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.082379397010484</v>
+        <v>2.095784524663316</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.714505505317021</v>
+        <v>4.727962799027239</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2156503444297471</v>
+        <v>-0.202198055709637</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.054344671686707</v>
+        <v>-2.040788625335104</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.804623339410419</v>
+        <v>-1.815052975108571</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>124</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.299889933113199</v>
+        <v>-3.287367643437577</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.68565709446456</v>
+        <v>-1.672747284888509</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.145280650551754</v>
+        <v>1.158287781969356</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.501340234772165</v>
+        <v>4.514319377170629</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.7371125680870847</v>
+        <v>0.750223372462024</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2281028928995212</v>
+        <v>0.2411457891938866</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.756272401433705</v>
+        <v>1.769338655734181</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.743169061863938</v>
+        <v>-2.7299880525687</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.228089116469903</v>
+        <v>1.241287855424666</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.1844155443452</v>
+        <v>1.197820671998031</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.205468671640517</v>
+        <v>4.218925965350735</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5988578484334113</v>
+        <v>-0.5854055597133012</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.825564072281537</v>
+        <v>-1.812008025929934</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.57584274000525</v>
+        <v>-1.586272375703402</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-6.197142023913678</v>
+        <v>-6.184619734238055</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.129748989858804</v>
+        <v>0.1427561212764061</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.573432759245982</v>
+        <v>1.586543563620921</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.870874696961643</v>
+        <v>1.883917593256008</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.712066905615295</v>
+        <v>2.725133159915771</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.384746122795832</v>
+        <v>-2.371565113500594</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5938941571262859</v>
+        <v>-0.5806954181715227</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.333758435623565</v>
+        <v>1.347163563276396</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.906782889083765</v>
+        <v>3.920240182793982</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.614389509126362</v>
+        <v>-1.600937220406252</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.886495971923111</v>
+        <v>-3.872939925571508</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.636774639646823</v>
+        <v>-3.647204275344976</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>101</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.948883864764426</v>
+        <v>-6.936361575088803</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.619863418322744</v>
+        <v>-2.606953608746693</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.04443509521636457</v>
+        <v>-0.03142796379876245</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.036313086896079</v>
+        <v>5.049292229294544</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.517693852021928</v>
+        <v>2.530804656396867</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.815135789737589</v>
+        <v>2.828178686031954</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.710600092267292</v>
+        <v>4.723666346567768</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.69717736592014</v>
+        <v>-1.683996356624903</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.22202076769954</v>
+        <v>0.2352195066543032</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.35209360247358</v>
+        <v>1.365498730126411</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.09783532766096</v>
+        <v>6.111292621371177</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.7984745843005356</v>
+        <v>-0.7850222955804256</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.198927215047419</v>
+        <v>-3.185371168695816</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.949205882771132</v>
+        <v>-2.959635518469284</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-8.445819272590931</v>
+        <v>-8.433296982915309</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.018945212493598</v>
+        <v>6.032011466794074</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4006191386688442</v>
+        <v>-0.3874381293736064</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>3.450160552025686</v>
+        <v>3.463565679678517</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>6.816835799136676</v>
+        <v>6.830293092846894</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.482114376851221</v>
+        <v>-1.468662088131111</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.902368987796123</v>
+        <v>-1.88881294144452</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.652647655519836</v>
+        <v>-1.663077291217988</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.023928884038703</v>
+        <v>5.036936015456305</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.535134397598583</v>
+        <v>7.548113539997047</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.3776655634788</v>
+        <v>9.390776367853739</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.35227854582694</v>
+        <v>14.36534480012742</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15.07557133752162</v>
+        <v>15.08875234681685</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.5860000227679</v>
+        <v>18.59919876172266</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.11682721869235</v>
+        <v>20.13023234634518</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.10255008485096</v>
+        <v>21.11600737856118</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>22.32740943267258</v>
+        <v>22.34086172139269</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>24.28810720268006</v>
+        <v>24.30166324903166</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>24.53782853495635</v>
+        <v>24.52739889925819</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>216</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.451006124234468</v>
+        <v>4.46352841391009</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.469062140899837</v>
+        <v>7.481971950475888</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.75937861948843</v>
+        <v>4.772385750906032</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.204446566910747</v>
+        <v>7.217425709309211</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.591951277764508</v>
+        <v>7.605062082139447</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.193548387096776</v>
+        <v>9.206614641397252</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.189327951278237</v>
+        <v>9.202508960573475</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.9801799169478</v>
+        <v>10.99337865590256</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.98190658377172</v>
+        <v>11.99531171142455</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.09196807426895</v>
+        <v>14.10542536797917</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>15.51524012050326</v>
+        <v>15.52869240922337</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>16.48387439844726</v>
+        <v>16.49743044479887</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>16.73359573072355</v>
+        <v>16.7231660950254</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>456</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.351128417702959</v>
+        <v>3.364038227279011</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.736961465492328</v>
+        <v>2.74996859690993</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.253179510380534</v>
+        <v>7.266158652778998</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.811249523378535</v>
+        <v>7.824360327753475</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.231498478638066</v>
+        <v>7.244541374932432</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.146764761365787</v>
+        <v>7.159831015666263</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.995370836268492</v>
+        <v>8.00855184556373</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.5922656869283</v>
+        <v>8.605464425883063</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.838631729970544</v>
+        <v>8.852036857623375</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.853176651267006</v>
+        <v>8.866633944977224</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.668261562998396</v>
+        <v>8.681713851718506</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.809410460825426</v>
+        <v>7.822966507177028</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.27843003871574</v>
+        <v>8.268000403017588</v>
       </c>
     </row>
     <row r="9">
@@ -4067,98 +4067,98 @@
         <v>780</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.865536038764382</v>
+        <v>1.878058328440005</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.45909063092833</v>
+        <v>3.472000440504381</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.936016796126609</v>
+        <v>2.949023927544211</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.989346851811035</v>
+        <v>5.0023259942095</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.245797431610669</v>
+        <v>6.258908235985608</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.158623984710935</v>
+        <v>6.171666881005301</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.714915908464306</v>
+        <v>6.727982162764782</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.145168407118696</v>
+        <v>7.158349416413934</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.34057877734665</v>
+        <v>7.353777516301413</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.77250487437</v>
+        <v>7.785910002022831</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.824161806462683</v>
+        <v>7.837619100172901</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.602134707397852</v>
+        <v>7.615586996117962</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.540854455427315</v>
+        <v>6.554410501778918</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.534165531293347</v>
+        <v>6.523735895595195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 26.43</t>
+          <t>X &lt; 26.42</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1065</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.640331558181046</v>
+        <v>0.6031961189983619</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.512965594915656</v>
+        <v>1.473847361902287</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.170222453012684</v>
+        <v>1.131104019736668</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.518844845226553</v>
+        <v>2.531823987625017</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.011351465205934</v>
+        <v>3.024462269580873</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.363126798969851</v>
+        <v>3.32183629921596</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.996967190515576</v>
+        <v>3.010033444816052</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.147335254355966</v>
+        <v>3.105816583393299</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.555818936248777</v>
+        <v>3.56901767520354</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.39583459629128</v>
+        <v>4.409239723944111</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.380394006783916</v>
+        <v>3.393846295504027</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.054036109454039</v>
+        <v>3.067592155805642</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.679344296190422</v>
+        <v>3.66891466049227</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>1373</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.052147786881193</v>
+        <v>1.02595309455603</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7103392616121553</v>
+        <v>0.6835852859531926</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3551918239972949</v>
+        <v>0.3284776864331675</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.322903312271052</v>
+        <v>1.295525548278619</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.260311219709351</v>
+        <v>1.232690798600657</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.743786824775739</v>
+        <v>1.715933934706328</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.627333916812539</v>
+        <v>1.599497720554844</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.419294281244568</v>
+        <v>1.39135478314023</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.54503516520915</v>
+        <v>1.516947679471578</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.4114202197675</v>
+        <v>2.382259794879182</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.061000471560632</v>
+        <v>2.07445776527085</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.168216840850711</v>
+        <v>2.181669129570821</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.966461865739753</v>
+        <v>1.980017912091355</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.361849621905328</v>
+        <v>2.351419986207176</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.244054322521045</v>
+        <v>1.197718460342635</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4886276427974963</v>
+        <v>0.4426446372969863</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2276355012911537</v>
+        <v>-0.2735558890249905</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3601935448991682</v>
+        <v>-0.4061766666516462</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6897596366897716</v>
+        <v>-0.7356458824623218</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1709752697895013</v>
+        <v>0.1249862888701614</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7683334497731664</v>
+        <v>0.7223329586513074</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8658448937526302</v>
+        <v>0.8199242482015308</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8379782830252864</v>
+        <v>0.7920404164212087</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.381972329991314</v>
+        <v>1.336205860011006</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7630178222417783</v>
+        <v>0.7510407880173275</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6198861866878005</v>
+        <v>0.607799046944578</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7913475520742637</v>
+        <v>0.7797145050580596</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.632784860681902</v>
+        <v>1.597516466711468</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>2042</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.599596263326319</v>
+        <v>0.586269948044027</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.06017762518202829</v>
+        <v>-0.07359262530300725</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7212360761433274</v>
+        <v>-0.7344368611797378</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.052554336431612</v>
+        <v>-1.065570841605421</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.711367414280396</v>
+        <v>-1.724206210543478</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.290294284519831</v>
+        <v>-1.30327399071448</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4696443610984105</v>
+        <v>-0.4830554974916339</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2260625124993254</v>
+        <v>-0.2397190515128642</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3090983588830554</v>
+        <v>-0.3227395150543302</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.09073458985999849</v>
+        <v>0.07667547127241647</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4781086103451742</v>
+        <v>-0.4919508732326889</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3674275618705849</v>
+        <v>-0.3813255382394942</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1427781601913694</v>
+        <v>0.1563342065429723</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6863290713119312</v>
+        <v>0.6758994356137791</v>
       </c>
     </row>
     <row r="14">
@@ -4324,101 +4324,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5951145955567654</v>
+        <v>0.584714366702265</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4758005128067566</v>
+        <v>0.4651332975681228</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1981080500604904</v>
+        <v>-0.2085675446539952</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4336413479937775</v>
+        <v>-0.4439808334202837</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7756385102060648</v>
+        <v>-0.7859413780681663</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.3353397428338667</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.08295418737028371</v>
+        <v>-0.09352965874704466</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.08011041485099923</v>
+        <v>0.06936650672941624</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1736754989362339</v>
+        <v>-0.1843285140056565</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3010257897079214</v>
+        <v>0.2899945607237839</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4866452462098749</v>
+        <v>-0.4973821229462771</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3412413609782092</v>
+        <v>-0.3520419042658105</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.06705152747866805</v>
+        <v>-0.05349548112706515</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5111966055888573</v>
+        <v>0.5194623913216887</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 46.86</t>
+          <t>X &lt; 46.85</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2547</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.535088448058886</v>
+        <v>0.5476107377345087</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3906878322675169</v>
+        <v>0.4035976418435681</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.100193506411415</v>
+        <v>-0.08718637499381288</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1442753944872592</v>
+        <v>-0.131296252088795</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.387500777030013</v>
+        <v>-0.3743899726550737</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3427915926639145</v>
+        <v>-0.3297486963695491</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2204448487758484</v>
+        <v>0.2335111030763244</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1666297044420588</v>
+        <v>0.1798107137372966</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3038844296410517</v>
+        <v>-0.2906856906862885</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.0832137733141991</v>
+        <v>0.09661890096703019</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.609512535410957</v>
+        <v>-0.5960552417007392</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3962954338894278</v>
+        <v>-0.3828431451693177</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3455924310195684</v>
+        <v>-0.3099246134395841</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.0440263026382226</v>
+        <v>0.07285854365777311</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.05266301511306892</v>
+        <v>-0.05895693473241437</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1732345543591478</v>
+        <v>-0.1796828845457838</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1895358121846158</v>
+        <v>-0.196029702249092</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2912947727041129</v>
+        <v>-0.297740318787838</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.1632607998774773</v>
+        <v>-0.1698211374078014</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.133799880528457</v>
+        <v>-0.1403388702527906</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2686882751862996</v>
+        <v>0.2619904055108861</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4330140627225418</v>
+        <v>0.4261966770669474</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.07593559381135151</v>
+        <v>-0.08258125506995384</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.04196009889943042</v>
+        <v>-0.04872476565728334</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5147135352945043</v>
+        <v>-0.5213367920923204</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2079831027199504</v>
+        <v>-0.2147167059436583</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3196450546756537</v>
+        <v>-0.3263933790249638</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1938528141068971</v>
+        <v>-0.1885004381263613</v>
       </c>
     </row>
     <row r="17">
@@ -4480,101 +4480,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.05810073203396371</v>
+        <v>-0.06318601038660887</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.02805258295480684</v>
+        <v>0.02277862883715187</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1219680997249739</v>
+        <v>0.1166211153026921</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.06883920433634216</v>
+        <v>0.0635197024620382</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.04763836232967122</v>
+        <v>-0.05297423258818412</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.06637841063495387</v>
+        <v>0.06103012455623968</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4376113662657772</v>
+        <v>0.4321268292243801</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5613818233321126</v>
+        <v>0.5558068899400723</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1149740239547654</v>
+        <v>0.1095402720641729</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.226890111774118</v>
+        <v>0.2213324441815558</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.09370394760124867</v>
+        <v>-0.09917680832112552</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.0944838956337648</v>
+        <v>0.08894781123814255</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.09795221994497183</v>
+        <v>0.09237063110789734</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.06318037609766236</v>
+        <v>0.06742941399360092</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 59.12</t>
+          <t>X &lt; 59.11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.02764131098312106</v>
+        <v>-0.0318066157760839</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1279606957245605</v>
+        <v>0.1236153437896661</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1005650781534086</v>
+        <v>0.09619460113118095</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2613472523862512</v>
+        <v>-0.2655945602440113</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.01390094326308144</v>
+        <v>0.009520680865563236</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1695079382335152</v>
+        <v>0.165099380331398</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5804006521766496</v>
+        <v>0.5758519475370463</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8961495688141454</v>
+        <v>0.8914604239909849</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5340519708198528</v>
+        <v>0.5294708705662003</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4675124832257325</v>
+        <v>0.4628821526791995</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.216969551967523</v>
+        <v>0.2124002433011967</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.460961704155892</v>
+        <v>0.4563147331112631</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6337141136015703</v>
+        <v>0.6289757832407474</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4864060490290782</v>
+        <v>0.4897416773148038</v>
       </c>
     </row>
     <row r="19">
@@ -4584,101 +4584,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.01727815253956777</v>
+        <v>0.01372737319995565</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3819712214965207</v>
+        <v>0.3781979376388023</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1263448504252551</v>
+        <v>0.1226211317692929</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1250672865074876</v>
+        <v>-0.1287071882942712</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1501977523199898</v>
+        <v>0.1464350517992656</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4338581035513087</v>
+        <v>0.4300265470902858</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7954570442201643</v>
+        <v>0.7915068012664221</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.11240705984369</v>
+        <v>1.108325820378063</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8845179566449488</v>
+        <v>0.8805003587652891</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.003415811759304</v>
+        <v>0.999301889447878</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.724054706355588</v>
+        <v>0.7200104781123287</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.021725868924506</v>
+        <v>1.017590398121371</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.110772347410361</v>
+        <v>1.106578763624597</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9786231128551393</v>
+        <v>0.9812871540069352</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 67.29</t>
+          <t>X &lt; 67.28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.137570599987562</v>
+        <v>-0.1403660012774779</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2568147647180368</v>
+        <v>0.2538153478680201</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1221353981895703</v>
+        <v>-0.125046810460951</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6789420941580531</v>
+        <v>-0.6816849679859374</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3812394635188241</v>
+        <v>-0.384100190854106</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.04941666213902352</v>
+        <v>0.04644431570069685</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3325105682753176</v>
+        <v>0.3294490819339231</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8492063047049783</v>
+        <v>0.8459664021839544</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6579663863153655</v>
+        <v>0.6547775914950336</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7045200423006719</v>
+        <v>0.7012697962327366</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4870805333673189</v>
+        <v>0.4838812886886146</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9198093991183498</v>
+        <v>0.9164833407477957</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.015608775996611</v>
+        <v>1.012230035934337</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8416167952663542</v>
+        <v>0.843740413837601</v>
       </c>
     </row>
     <row r="21">
@@ -4688,153 +4688,153 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.03303108039096969</v>
+        <v>-0.03534068419565273</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4070106976602759</v>
+        <v>0.4045042112434416</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2539393941850392</v>
+        <v>0.2514574676015187</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1947053446951728</v>
+        <v>-0.197055835053483</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1232242601743394</v>
+        <v>-0.1256200576850617</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2463742406854905</v>
+        <v>0.243885715398541</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.3754810279529295</v>
+        <v>0.3729509011914587</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7173287489021618</v>
+        <v>0.7146797716111521</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5871338096159704</v>
+        <v>0.5845176838508763</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6034136877001401</v>
+        <v>0.6007538882952872</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4430951514311943</v>
+        <v>0.4404703647763668</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8056262513149335</v>
+        <v>0.8028988334581655</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9690974194251041</v>
+        <v>0.9663035732464635</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.894559135229386</v>
+        <v>0.8962438265594272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 75.46</t>
+          <t>X &lt; 75.45</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3613</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.04379278844970003</v>
+        <v>0.05631507812532277</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.5984363426878332</v>
+        <v>0.6113461522638843</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4394129584631727</v>
+        <v>0.4248262708962258</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.03280141914084567</v>
+        <v>0.04578056153930987</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.08919037218747405</v>
+        <v>0.1023011765624133</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4018207216939231</v>
+        <v>0.4148636179882885</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4151567357769466</v>
+        <v>0.4005986806851638</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7645277711589102</v>
+        <v>0.7500768379285958</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7189858870970482</v>
+        <v>0.7045450461734148</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7137438952330228</v>
+        <v>0.6995018014316088</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6076596508012386</v>
+        <v>0.59346207725482</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9344040977585308</v>
+        <v>0.9201938691895677</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.05570411416187</v>
+        <v>1.0415899889584</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.016944953181543</v>
+        <v>1.006515317483391</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 79.55</t>
+          <t>X &lt; 79.54</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.08248358868372918</v>
+        <v>0.08075379868765964</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6278331983690322</v>
+        <v>0.6259022147966178</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3834617367891298</v>
+        <v>0.3815832315437078</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1215529541663898</v>
+        <v>0.119748813748437</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1951000291217326</v>
+        <v>0.1932574688423045</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.398896337934687</v>
+        <v>0.3970072301241601</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4920576513855153</v>
+        <v>0.4901395456118109</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8820292099941724</v>
+        <v>0.879988993566819</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8634327349832134</v>
+        <v>0.8613945936006502</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8168103921737639</v>
+        <v>0.8147561558689915</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6547135277158773</v>
+        <v>0.6526956608324994</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.9493450168056086</v>
+        <v>0.9472471793279027</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.007108187187036</v>
+        <v>1.004979876199265</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.945991800262469</v>
+        <v>0.9471615812624421</v>
       </c>
     </row>
     <row r="24">
@@ -4844,101 +4844,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1901397839288776</v>
+        <v>0.1885981178906349</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.5958427676804732</v>
+        <v>0.5941462075099651</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2957378480731592</v>
+        <v>0.2941093976296898</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.01305555002534931</v>
+        <v>0.01150552249135472</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1574417883231902</v>
+        <v>0.1558370687776076</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2557033759079772</v>
+        <v>0.2540800572436623</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3728595516981272</v>
+        <v>0.3712016883372442</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.749728640892414</v>
+        <v>0.7479558517010361</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7839688544000936</v>
+        <v>0.7821843154947317</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7518328269313628</v>
+        <v>0.7500317780258072</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4551987748490518</v>
+        <v>0.4534704151676863</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7190231751165399</v>
+        <v>0.7172243146227544</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.823001899910679</v>
+        <v>0.8211623180754586</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8469695547082949</v>
+        <v>0.8479887478416188</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 87.72</t>
+          <t>X &lt; 87.71</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1644564166321274</v>
+        <v>0.1631250112967493</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4093339473206328</v>
+        <v>0.407897876401826</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1078076172065394</v>
+        <v>0.1064405216546831</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.08993301150886168</v>
+        <v>-0.09124552116296059</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.01818942318073624</v>
+        <v>0.01683453407518698</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.06660006660006701</v>
+        <v>0.06523906224872178</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1807796879812145</v>
+        <v>0.1793858315597561</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.518994686296935</v>
+        <v>0.5174994914311597</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4990500529065329</v>
+        <v>0.4975578944609182</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5077279736131501</v>
+        <v>0.5062118520715231</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2651333239513463</v>
+        <v>0.263675414385375</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5783614365937098</v>
+        <v>0.5768210127609521</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6482922481871753</v>
+        <v>0.6467222544232101</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.6490863467686907</v>
+        <v>0.6499915477220171</v>
       </c>
     </row>
     <row r="26">
@@ -4948,153 +4948,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3838</v>
+        <v>3839</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2201425678710365</v>
+        <v>0.2189801273057341</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4391884502787278</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.007783688626162188</v>
+        <v>0.006632985153274262</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1336607711965883</v>
+        <v>-0.1347725528656696</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.01786757617885115</v>
+        <v>0.01670449378185879</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.00842269715634103</v>
+        <v>-0.009573246166716842</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1551146347488555</v>
+        <v>0.1539192002462784</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4045936852744703</v>
+        <v>0.4033229084615471</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.4100957812898898</v>
+        <v>0.4088216743632671</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4073505076539448</v>
+        <v>0.4060585238107066</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.2420825874057755</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5007725279106836</v>
+        <v>0.4994513743848401</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.5120742575926727</v>
+        <v>0.5107406299840491</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4900854147796707</v>
+        <v>0.4908814529986358</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 95.89</t>
+          <t>X &lt; 95.88</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3894</v>
+        <v>3895</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2068432257332091</v>
+        <v>0.2058802847164216</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2216649741478349</v>
+        <v>0.2206698241878371</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1592916512945095</v>
+        <v>-0.1601966010311529</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3737258678190685</v>
+        <v>-0.3745741010004551</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1809157476005936</v>
+        <v>-0.1818231637621963</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1769830018442775</v>
+        <v>-0.177886716818854</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.06832178864163296</v>
+        <v>-0.06925528285811566</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1451684071186889</v>
+        <v>0.1441715921874049</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1752964235544283</v>
+        <v>0.1742903368142379</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1603171646964086</v>
+        <v>0.1592996285543009</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.004345329203808035</v>
+        <v>-0.005324684279351288</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2498206969729679</v>
+        <v>0.2487762343880391</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.331875159156624</v>
+        <v>0.3308018038375735</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2623864629041037</v>
+        <v>0.2630795643355341</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 99.98</t>
+          <t>X &lt; 99.97</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3940</v>
+        <v>3941</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1501235315481821</v>
+        <v>0.1493318197438498</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1206965688500645</v>
+        <v>0.1198887693944855</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1338973444025626</v>
+        <v>-0.1346467877054423</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2430452286823055</v>
+        <v>-0.2437655502875131</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1093655112960121</v>
+        <v>-0.1101277912782663</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.05133626780250466</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.02976717492438041</v>
+        <v>0.02897195311626888</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2100052428627777</v>
+        <v>0.2091572354001201</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1376929432821115</v>
+        <v>0.1368619770341297</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.138318573855102</v>
+        <v>0.1374747870476938</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.001455808655308033</v>
+        <v>-0.002267517604181535</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2247784259319872</v>
+        <v>0.2239094370551697</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2755892292384701</v>
+        <v>0.2747008659048973</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2351937754688009</v>
+        <v>0.2357639504296429</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3980</v>
+        <v>3981</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1987730496873468</v>
+        <v>0.198102497257338</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.178555201094305</v>
+        <v>0.177870328192455</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.05237374926718275</v>
+        <v>-0.0530057728822797</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1841638480154515</v>
+        <v>-0.1847616195882154</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.08227785234329588</v>
+        <v>-0.08290784267258289</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.02184048562314445</v>
+        <v>-0.02248241417181873</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.032525061287906</v>
+        <v>0.03186817979020873</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.256442481764573</v>
+        <v>0.2557235747361801</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1089730764812202</v>
+        <v>0.1082901052344738</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1261502250033075</v>
+        <v>0.1254525172240761</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.08614703857093531</v>
+        <v>0.08545660403450483</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3104760897723935</v>
+        <v>0.309729409065298</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3565752832054159</v>
+        <v>0.3558116788707082</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3442415524246414</v>
+        <v>0.3446738122377013</v>
       </c>
     </row>
     <row r="30">
@@ -5159,46 +5159,46 @@
         <v>4004</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2324765416272143</v>
+        <v>0.2201046316513597</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2525577879413063</v>
+        <v>0.240567199110977</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.02066730543465667</v>
+        <v>0.008767836603190915</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.08462501588279991</v>
+        <v>-0.07164587348433571</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.03837539936929346</v>
+        <v>0.05148620374423274</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.07533538895972924</v>
+        <v>0.08837828525409464</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.05409854084065557</v>
+        <v>0.06716479514113161</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2489474211221463</v>
+        <v>0.2621284304173841</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.07704992239848707</v>
+        <v>0.09024866135325027</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1139757787151581</v>
+        <v>0.1273809063679892</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.02307012715787238</v>
+        <v>0.03652742086809013</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.246245464339367</v>
+        <v>0.2596977530594771</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3145027796374364</v>
+        <v>0.3280588259890393</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2787542758820862</v>
+        <v>0.2932996651589619</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1407442175095426</v>
+        <v>0.1402511306921568</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1503072157619343</v>
+        <v>0.149797455921977</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.03316448040433073</v>
+        <v>-0.03363253853630255</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1617067150841081</v>
+        <v>-0.1621420544456313</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.04298311193591076</v>
+        <v>-0.04345276934569853</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.004366071295464735</v>
+        <v>-0.004842917688208104</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.05080247850749231</v>
+        <v>-0.05126879924993233</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1645325910022137</v>
+        <v>0.1640086073592215</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.006671246483300308</v>
+        <v>-0.007153590913134167</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.02451662068021676</v>
+        <v>0.02401885723206476</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06714516741310206</v>
+        <v>-0.06762224582204368</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1051872104503602</v>
+        <v>0.1046674668498184</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1702586243998283</v>
+        <v>0.1697188045872267</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1611299647093958</v>
+        <v>0.1614729208291195</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.09276857634174718</v>
+        <v>0.09234178773700563</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.09553007224581478</v>
+        <v>0.09508999462842382</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.03955535637999219</v>
+        <v>-0.03996540290852835</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1177172286323867</v>
+        <v>-0.1181072114873842</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.001737085154630336</v>
+        <v>-0.002160003145242229</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.03797521301407869</v>
+        <v>0.03754459303686275</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.01605565015658073</v>
+        <v>0.01562957494979855</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1545251988589058</v>
+        <v>0.1540611541089021</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.05781876013450926</v>
+        <v>0.05737788829556933</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.06063885838154448</v>
+        <v>0.06019050927471881</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.03148871585450053</v>
+        <v>-0.0319161206336176</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1155758229629527</v>
+        <v>0.1151121623098064</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1539080684809306</v>
+        <v>0.153431469285934</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1458627048882235</v>
+        <v>0.1461641919365348</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1562182057959092</v>
+        <v>0.1558266724335127</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1526567784822035</v>
+        <v>0.1522550893556911</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.007980787046228954</v>
+        <v>-0.008345900991258759</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.08531618872482483</v>
+        <v>-0.0856616195513098</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.02101532341427514</v>
+        <v>-0.02138034359096963</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.004858811048947587</v>
+        <v>-0.005225970740198704</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.002465808917413881</v>
+        <v>-0.002834306445208767</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1336176575487826</v>
+        <v>0.1332123912769063</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.11079283074654</v>
+        <v>0.1103925732359556</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.06109408206420852</v>
+        <v>0.06070010867135522</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.006882374802842151</v>
+        <v>-0.007261205981073715</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1397446988823887</v>
+        <v>0.1393298543418879</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2008837306140734</v>
+        <v>0.2004508083358232</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1938650081230264</v>
+        <v>0.1941124350662236</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4070</v>
+        <v>4071</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1639214642622235</v>
+        <v>0.1635501790640745</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1086088409561015</v>
+        <v>0.1082407615352992</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.00343369049368647</v>
+        <v>-0.003776987040140511</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1049216248103875</v>
+        <v>-0.1052393963747562</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.04165990144608145</v>
+        <v>-0.04199674138995846</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.0250256172809884</v>
+        <v>-0.02536481982635053</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.0473149928394534</v>
+        <v>-0.04764943140531841</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1122552947158937</v>
+        <v>0.1118785951086707</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.08935964882691394</v>
+        <v>0.08898800421062703</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.06282623685631705</v>
+        <v>0.06245554237206363</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.05448871888560802</v>
+        <v>-0.05483209124736277</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1164916667449987</v>
+        <v>0.1161063638114115</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1767972402278772</v>
+        <v>0.1763942809336214</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1702141673419888</v>
+        <v>0.1704490448875617</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1650982651558834</v>
+        <v>0.1647801411310965</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1277277594337249</v>
+        <v>0.1274100715237765</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.08772306935557594</v>
+        <v>0.0874129029666193</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03718913762463671</v>
+        <v>-0.0374682769171315</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.02523622223549182</v>
+        <v>-0.0255212715339681</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.03185220576525438</v>
+        <v>-0.03213420072546569</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05440254380480525</v>
+        <v>-0.05467961989700854</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.07813087587398826</v>
+        <v>0.07781880877048053</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.006192733283185703</v>
+        <v>0.005897771646687033</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.02510438925258285</v>
+        <v>0.02480014413877996</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04368346969554437</v>
+        <v>-0.04397213512158515</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1267316560593699</v>
+        <v>0.1264013651230442</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1361176397315944</v>
+        <v>0.1357826634885697</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1305907193505433</v>
+        <v>0.1307909410064099</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_7.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_7.xlsx
@@ -575,1294 +575,1294 @@
         <v>132</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.302023651315309</v>
+        <v>1.272940737476844</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.004549880311657</v>
+        <v>8.003435392253188</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.590970365877574</v>
+        <v>4.590854334954926</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.988979766735213</v>
+        <v>6.988537263561</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.453625049800358</v>
+        <v>6.502101392094914</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.239913990333164</v>
+        <v>5.263853668740069</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5.912924424921563</v>
+        <v>5.960880789895874</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.448091106857426</v>
+        <v>5.497287501660054</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.145181301914874</v>
+        <v>6.218367634466517</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.811336080234732</v>
+        <v>6.910601936769353</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.636582296048047</v>
+        <v>9.736434800570535</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.1878361240982</v>
+        <v>11.31148570463525</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.52808472242367</v>
+        <v>11.67674459852321</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.75683612869542</v>
+        <v>11.92883488826174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 16.21</t>
+          <t>X ≈ 16.2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>240</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.812286241381976</v>
+        <v>-0.841378228204924</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3421670204552498</v>
+        <v>-0.3433463794491871</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9262681632772995</v>
+        <v>0.9261277757851545</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.289398860590339</v>
+        <v>7.288969218879394</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.001397748526671</v>
+        <v>8.049882642970907</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.637318853441855</v>
+        <v>6.6612688711825</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.306918018410776</v>
+        <v>5.354868713055893</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.922120219269438</v>
+        <v>6.971321073064253</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.446991632707288</v>
+        <v>6.520174506140137</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.016016066806394</v>
+        <v>6.115273403847318</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.147832054582246</v>
+        <v>4.247668185987877</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.517675520568396</v>
+        <v>2.641308367639624</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.01572935746414572</v>
+        <v>0.1643780223211024</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.6583512802103897</v>
+        <v>0.8303500397774286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 20.3</t>
+          <t>X ≈ 20.29</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>324</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.139689550527592</v>
+        <v>2.110650083121783</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.609890236990289</v>
+        <v>3.608757174471144</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.21763403916313</v>
+        <v>3.217521630188578</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.808302125348213</v>
+        <v>1.807842170451565</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.042472082449031</v>
+        <v>4.090923923210418</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.648754522179722</v>
+        <v>4.67269629918556</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.105941185992691</v>
+        <v>6.153892910104041</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.949644473704851</v>
+        <v>5.998838417880059</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.58251373547936</v>
+        <v>5.65568522825766</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.276878002312344</v>
+        <v>6.376125233043794</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.382862899036766</v>
+        <v>6.482695596513878</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.110943613348752</v>
+        <v>6.234573685561152</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.767378422628376</v>
+        <v>4.916024958499122</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.068845107371075</v>
+        <v>4.240843866937595</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 24.38</t>
+          <t>X ≈ 24.37</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>285</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.861367150083787</v>
+        <v>-2.907274916912108</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.955395935571786</v>
+        <v>-4.170139886556107</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.817102771910875</v>
+        <v>-3.524271563502502</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.19598847302327</v>
+        <v>-4.082934913315476</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.786722763113865</v>
+        <v>-5.629667294882672</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.438887781469894</v>
+        <v>-4.113110133208046</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.138753286086747</v>
+        <v>-7.142326754833817</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.958659361869387</v>
+        <v>-8.12795264394601</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.780894350416638</v>
+        <v>-7.276055031975254</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.828111380620825</v>
+        <v>-5.462130582071389</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.487412282069769</v>
+        <v>-7.773354526800539</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.156193166952434</v>
+        <v>-8.418795416425553</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.473642880176534</v>
+        <v>-7.221615019323046</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.144280298736703</v>
+        <v>-4.674035925135037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 28.47</t>
+          <t>X ≈ 28.45</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.511884982318932</v>
+        <v>2.825874171644607</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.039157886276321</v>
+        <v>-1.777882999627209</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.440736336881336</v>
+        <v>-2.639785191888805</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.950414664595158</v>
+        <v>-2.966400681841911</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.941186979470288</v>
+        <v>-5.503443280146001</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.817203305702066</v>
+        <v>-4.279059254348923</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.255205382334225</v>
+        <v>-3.708223944677968</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.523311698655462</v>
+        <v>-4.809808084483535</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.556928909911719</v>
+        <v>-5.795742069796837</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.610930374164148</v>
+        <v>-5.040740725262928</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.664849538184072</v>
+        <v>-4.44040922541361</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.009092293938927</v>
+        <v>-2.942313266982389</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.780281752556157</v>
+        <v>-2.388104104938471</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.204202832343604</v>
+        <v>-2.771970635328245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 32.55</t>
+          <t>X ≈ 32.53</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.946486046036803</v>
+        <v>1.775602460827379</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6106819574019866</v>
+        <v>-0.759955576709423</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.901293258765783</v>
+        <v>-2.740995152325787</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.828938171827751</v>
+        <v>-7.690476190476197</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.314760073642013</v>
+        <v>-9.132106283809144</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-6.805472316589267</v>
+        <v>-6.637098542767916</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.097081607490047</v>
+        <v>-2.888230822469495</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.667018302715249</v>
+        <v>-1.449301678091004</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.360105013124148</v>
+        <v>-2.121194922148433</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.209506996672786</v>
+        <v>-2.945023502963416</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.994146531659815</v>
+        <v>-4.736465537801102</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.226299905993883</v>
+        <v>-5.948140070277397</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.434076043016091</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.678146610084774</v>
+        <v>-1.332348372921167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 36.64</t>
+          <t>X ≈ 36.61</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.347905240082525</v>
+        <v>-2.510111824887048</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.554816125945777</v>
+        <v>-2.398373655805678</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.953765950288549</v>
+        <v>-3.074597519826533</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.239306722767218</v>
+        <v>-4.357142857142925</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.480484892751598</v>
+        <v>-6.541307252332068</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.160795784043231</v>
+        <v>-7.963436987750491</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.26197140695983</v>
+        <v>-6.046691947032386</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.315363354473497</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.660125460147761</v>
+        <v>-5.419553813727603</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.946244953803458</v>
+        <v>-5.678410643130221</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-6.43723312496784</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.112070691969095</v>
+        <v>-4.976926726182839</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.825202666037455</v>
+        <v>-2.829711771390663</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.733763922811143</v>
+        <v>-3.710610412200154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 40.73</t>
+          <t>X ≈ 40.7</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>262</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5719022199112018</v>
+        <v>0.5433232896168363</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.684099114987035</v>
+        <v>4.303657654842752</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.908354711118463</v>
+        <v>3.909919666528005</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.420180566780154</v>
+        <v>4.039803707742635</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6.55284492101358</v>
+        <v>6.222310291981557</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.231342616072496</v>
+        <v>6.495095810800649</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.950053840454103</v>
+        <v>2.235966439132277</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.483110735259345</v>
+        <v>1.770133678748934</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.8963283156845989</v>
+        <v>0.2064435123601385</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.954036463945421</v>
+        <v>1.291011878110126</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5391140117086906</v>
+        <v>-1.203204905303821</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1233360090271205</v>
+        <v>-0.7633587786258644</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.687962598221375</v>
+        <v>-2.303554873128796</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6997912134280924</v>
+        <v>-1.67283062180028</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 44.81</t>
+          <t>X ≈ 44.78</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.193405443473246</v>
+        <v>0.3587406341293615</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1828203182977148</v>
+        <v>0.005071745694870344</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.068177494270167</v>
+        <v>0.8408419541014283</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.843612439539413</v>
+        <v>3.019906323185005</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.53972382209453</v>
+        <v>3.760165378954405</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2760911806025348</v>
+        <v>-0.06540975796452386</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.340525646401076</v>
+        <v>3.562458742974094</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.228543351567595</v>
+        <v>1.457281720295626</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.299792828712356</v>
+        <v>-1.038707282283745</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.738277552118142</v>
+        <v>-1.452699797524957</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.530985241811869</v>
+        <v>-1.247004179487327</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6741996223720932</v>
+        <v>-0.3691653109748927</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.739395749236429</v>
+        <v>-1.993831434259896</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.161607567526055</v>
+        <v>-3.793966900113567</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 48.89</t>
+          <t>X ≈ 48.86</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>227</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-6.893246497451337</v>
+        <v>-7.135662485679887</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.75098774329139</v>
+        <v>-6.956725033390853</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.423492654280324</v>
+        <v>-1.623590775009525</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.174324779414427</v>
+        <v>-2.37476400251731</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.12913672817222</v>
+        <v>1.981801834504338</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.987336762543137</v>
+        <v>2.254587353323267</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5842916340262363</v>
+        <v>1.312873995375341</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.198485080393368</v>
+        <v>3.930741675520679</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.252652665676401</v>
+        <v>3.01271179766136</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.682050282459656</v>
+        <v>-0.8948172236822529</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3102022468786316</v>
+        <v>1.103685500587929</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.667791869234073</v>
+        <v>2.042909506675237</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5158281606212398</v>
+        <v>-0.9954202260560407</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.121017295413502</v>
+        <v>-3.389547170208075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 52.98</t>
+          <t>X ≈ 52.94</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1248950881260953</v>
+        <v>0.6148881751129593</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.975960703626946</v>
+        <v>3.719211089957106</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.675430156568247</v>
+        <v>5.40880643497573</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.329215509580685</v>
+        <v>6.059523809523803</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.649564699940434</v>
+        <v>2.445274668571884</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.994059148423752</v>
+        <v>3.238893520724204</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.909348789157583</v>
+        <v>2.657404098165294</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.442280145370781</v>
+        <v>2.191571337782008</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.904858198272152</v>
+        <v>2.675432061978604</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.149180239638625</v>
+        <v>3.934936814496901</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.038719919074772</v>
+        <v>5.814129700294082</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.502417443157903</v>
+        <v>4.830629770992367</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.176507427540763</v>
+        <v>7.039638511095205</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.784442030646879</v>
+        <v>4.684516706443908</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 57.07</t>
+          <t>X ≈ 57.02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5311321622368013</v>
+        <v>0.1844989535562007</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.931994261943984</v>
+        <v>1.595333844448255</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2700060384736389</v>
+        <v>-0.5948113294951298</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.163877280427506</v>
+        <v>-6.452951240376393</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.129158467681613</v>
+        <v>0.8422307563961624</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.028942135870928</v>
+        <v>1.713818670424743</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.149051053713251</v>
+        <v>2.850767371618581</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>6.898849879805972</v>
+        <v>6.576551377702103</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8.042687000391624</v>
+        <v>7.737183558984462</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.783129649844895</v>
+        <v>4.518145397331232</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.783247768693208</v>
+        <v>5.511609740214368</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7.022445198156895</v>
+        <v>6.767381267998353</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>10.21675217616871</v>
+        <v>9.965037712691945</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8.032849272178389</v>
+        <v>7.818872993868986</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 61.16</t>
+          <t>X ≈ 61.11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.177620554831506</v>
+        <v>2.111736914608812</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>6.883507632499381</v>
+        <v>6.41091277062943</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7976793371750901</v>
+        <v>0.1348218411381197</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.366928871007502</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.641647447993201</v>
+        <v>3.136801279216236</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>7.191053997953397</v>
+        <v>6.7709313358502</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.293335508605878</v>
+        <v>5.869939112170862</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>6.639274994900582</v>
+        <v>6.244442486241446</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9.830325358702964</v>
+        <v>8.728478280465993</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>14.67146347294216</v>
+        <v>13.78700264082742</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>13.65375418460057</v>
+        <v>12.74252605883746</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>15.31414859711864</v>
+        <v>14.48136506511002</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>13.26798148364263</v>
+        <v>12.40553486963872</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13.49371713386925</v>
+        <v>12.65457973165409</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 65.24</t>
+          <t>X ≈ 65.19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.474293513978097</v>
+        <v>-5.141690772255409</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.436472984525338</v>
+        <v>-2.777499436358625</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.480250991796929</v>
+        <v>-5.144921635199609</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-12.63479406012913</v>
+        <v>-12.25187969924813</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-11.84858030196651</v>
+        <v>-10.76744462967373</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.239947994185734</v>
+        <v>-7.205185426644235</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.649161664710213</v>
+        <v>-9.239525726396046</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.818217063463798</v>
+        <v>-4.442200592042511</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.216947564357483</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.729118016316434</v>
+        <v>-3.98721230831012</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.609315863318358</v>
+        <v>-2.875563282161963</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.263679432817376</v>
+        <v>-0.1858175974286524</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.021578630501565</v>
+        <v>0.07691921284963854</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.120346291533387</v>
+        <v>-0.9898253988192423</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 69.33</t>
+          <t>X ≈ 69.27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.981268843415272</v>
+        <v>3.323221508446352</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>5.073377756623785</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>11.05934497904179</v>
+        <v>10.51297310164246</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.71057852599149</v>
+        <v>13.14285714285714</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.289936031719279</v>
+        <v>5.986941335238548</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.906637792446801</v>
+        <v>4.593060187390769</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.620246760911726</v>
+        <v>1.199070764832022</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.04850255514387</v>
+        <v>-3.433428662217942</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.428812442759131</v>
+        <v>-2.637067938021495</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.278731239088991</v>
+        <v>-3.460896518836435</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8027601284416193</v>
+        <v>-1.998370299705904</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.44905424499386</v>
+        <v>-1.940203562341011</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3481966949459263</v>
+        <v>0.1646385110951627</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.398547358641956</v>
+        <v>2.080350039777187</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 73.41</t>
+          <t>X ≈ 73.35</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.698859250364528</v>
+        <v>4.15655484177968</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>8.829246191008622</v>
+        <v>10.35115553440166</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>7.310879300635605</v>
+        <v>7.735195323864616</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9.688295455459858</v>
+        <v>11.1984126984127</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.150005902364164</v>
+        <v>9.598052446349719</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>7.200188920763296</v>
+        <v>7.648615742946305</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.497501033407246</v>
+        <v>2.032404098165351</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.154027895238421</v>
+        <v>3.788793560004237</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.463832255569642</v>
+        <v>5.974043173089719</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.613913459239782</v>
+        <v>6.261325703385786</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>6.656403312215474</v>
+        <v>8.279407478071917</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.567185958952884</v>
+        <v>6.115351993214659</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.023439600021504</v>
+        <v>4.609082955539655</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.372770755866007</v>
+        <v>7.080350039777308</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 77.5</t>
+          <t>X ≈ 77.43</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>63</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.487337937719523</v>
+        <v>1.45814214336707</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.463453431957291</v>
+        <v>-0.1250349417888685</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.105921127400926</v>
+        <v>-2.106074517404977</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.373510365393876</v>
+        <v>2.78571428571437</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.422522399599764</v>
+        <v>5.471068319365536</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6293099199714973</v>
+        <v>-0.6053525110216995</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5.635186069968682</v>
+        <v>5.683197748959088</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>8.342720600785114</v>
+        <v>6.804666575877164</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>9.869040031563927</v>
+        <v>9.942297141343538</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7.431819647932478</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.052515315069201</v>
+        <v>2.565121763786294</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.499591880122857</v>
+        <v>1.03598691384942</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-2.533774187317491</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.456728084868836</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 81.59</t>
+          <t>X ≈ 81.52</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>57</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>7.168206776483288</v>
+        <v>8.893396947042689</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.460523176229763</v>
+        <v>0.2926760022379113</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.364066490809364</v>
+        <v>-3.609833915901497</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.988227312133283</v>
+        <v>-5.234335839599098</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.263358970492177</v>
+        <v>-0.4604270858141746</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-8.983528800506171</v>
+        <v>-7.205185426644327</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.313853194860108</v>
+        <v>-5.51145555095755</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-7.780921838646798</v>
+        <v>-5.97728831134075</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.333132065345005</v>
+        <v>-4.259874955565309</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.428664896762633</v>
+        <v>-3.32931757146806</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-12.40529587958419</v>
+        <v>-12.30538784356561</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-14.12530369214119</v>
+        <v>-14.0016070711129</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-11.03668261563004</v>
+        <v>-10.88799306785221</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.54778907066661</v>
+        <v>-5.375790311100005</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 85.67</t>
+          <t>X ≈ 85.6</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>55</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.571825121443446</v>
+        <v>-1.601020915795971</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-12.27392030541637</v>
+        <v>-12.27510709186102</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-12.66869169017141</v>
+        <v>-12.66884508017573</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.083921092037585</v>
+        <v>-7.084415584415538</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-9.440392463315042</v>
+        <v>-9.391846543549327</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-12.77938207004365</v>
+        <v>-12.75542466109409</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-12.86409242930976</v>
+        <v>-12.81608075031944</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-15.14934289127837</v>
+        <v>-16.91827714706653</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-18.84668868416478</v>
+        <v>-18.77343157438504</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-16.06024384413096</v>
+        <v>-15.96089651883634</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-12.62858136602757</v>
+        <v>-12.52867333000889</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-8.957839577308555</v>
+        <v>-8.83414295628036</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-11.19617224880378</v>
+        <v>-11.0474827010259</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-12.78861841675906</v>
+        <v>-12.61661965719235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 89.75</t>
+          <t>X ≈ 89.68</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>51</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.38182906750486</v>
+        <v>2.391848959426689</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.770642974441031</v>
+        <v>0.8086718742708356</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.428049978941459</v>
+        <v>-7.42820336894578</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.376256207902117</v>
+        <v>-3.376750700280176</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.007022866453176846</v>
+        <v>-1.905215527506542</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.577956045088214</v>
+        <v>-7.514782949864092</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-3.653870411638628</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.090519361866612</v>
+        <v>-8.041271799472895</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.190717204663898</v>
+        <v>-6.117460094884258</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-7.040636000993757</v>
+        <v>-6.94128867569929</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.362984218077472</v>
+        <v>-1.263076182058853</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.250174693173136</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-9.591894173937526</v>
+        <v>-7.482420312434265</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-11.32694283743648</v>
+        <v>-9.194159764144381</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 93.84</t>
+          <t>X ≈ 93.76</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>56</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6952017448200607</v>
+        <v>-0.724397539172692</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-14.8063878378839</v>
+        <v>-14.80757462432855</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-11.62973065121031</v>
+        <v>-13.41559832692897</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-16.85664836476486</v>
+        <v>-18.64285714285715</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-13.82350934643193</v>
+        <v>-11.98924914095193</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-11.74042103108255</v>
+        <v>-11.716463622133</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-15.3965599617773</v>
+        <v>-15.34854828278703</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-17.64934289127837</v>
+        <v>-17.60009532888461</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-15.92461076208686</v>
+        <v>-15.85135365230712</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-16.77452955841667</v>
+        <v>-16.6751822331221</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-16.97923071667687</v>
+        <v>-16.87932268065819</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-16.94485256432159</v>
+        <v>-18.60687022900758</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-12.0078605604922</v>
+        <v>-13.6448852984286</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-15.35355348169418</v>
+        <v>-16.96726900784176</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 97.92</t>
+          <t>X ≈ 97.84</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>46</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.654829074012646</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.439928210554704</v>
+        <v>-6.267201953521095</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.034865622081504</v>
+        <v>4.208625275555441</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>10.8607429395829</v>
+        <v>13.03416149068329</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.974627299530759</v>
+        <v>6.02317321929646</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>10.61982741612223</v>
+        <v>12.8176978685503</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.361204013377865</v>
+        <v>10.58312873584651</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.720222326112939</v>
+        <v>7.943382931984843</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.036412004322855</v>
+        <v>-0.7892418510649861</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.712417757174542</v>
+        <v>0.5608426115983463</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2567941280435235</v>
+        <v>2.530615207540521</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.882740763079362</v>
+        <v>0.4148689014270559</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.476804659870957</v>
+        <v>-2.154202068614907</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.077155966166238</v>
+        <v>0.2687558368785972</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 102</t>
+          <t>X ≈ 101.9</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>40</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.01908396946569</v>
+        <v>4.989888175113009</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>5.906711089957163</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.013126491646744</v>
+        <v>8.012973101642523</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.643351635235248</v>
+        <v>5.642857142857068</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.605062082139376</v>
+        <v>2.65360800190529</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.902436111774605</v>
+        <v>2.926393520724076</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3177257525083235</v>
+        <v>0.3657374314986939</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.710325047801177</v>
+        <v>-2.637067938021453</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.060243844131051</v>
+        <v>-0.960896518836428</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.735054997608799</v>
+        <v>8.834963033627474</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>8.769433149964122</v>
+        <v>8.893129770992395</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.349282296650713</v>
+        <v>8.497971844428513</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>11.07501794687725</v>
+        <v>11.24701670644395</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 106.1</t>
+          <t>X ≈ 106</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>23</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.040823099900429</v>
+        <v>4.011627305547741</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.12528918074965</v>
+        <v>11.12410239430499</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>10.73051779599466</v>
+        <v>10.73036440599029</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>19.55639511349595</v>
+        <v>19.555900621118</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>23.36593164735684</v>
+        <v>19.06665148016608</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>19.31547959003539</v>
+        <v>14.99161091202849</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.187290969899728</v>
+        <v>1.887476561933468</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.372396239156409</v>
+        <v>1.421643801550125</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.036412004322891</v>
+        <v>-7.310980981499711</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4614952863038368</v>
+        <v>-3.786983475358177</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-8.438858045869459</v>
+        <v>-12.68677609680731</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-8.4044798935142</v>
+        <v>-8.280783272485891</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.476804659871028</v>
+        <v>-8.675941199049717</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-8.598895096601076</v>
+        <v>-8.42689633703435</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 110.2</t>
+          <t>X ≈ 110</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-11.74017528979361</v>
+        <v>-13.22439753917265</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-13.35136138285744</v>
+        <v>-14.80757462432855</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.338725360205075</v>
+        <v>-8.058455469786111</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-13.61590762402412</v>
+        <v>-15.07142857142858</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-14.15419717711986</v>
+        <v>-11.98924914095198</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-13.85682314748473</v>
+        <v>-11.716463622133</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-17.6452372104546</v>
+        <v>-15.34854828278703</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-14.40860215053763</v>
+        <v>-15.81438104317037</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-14.46958430706041</v>
+        <v>-12.2799250808786</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-15.31950310339027</v>
+        <v>-13.10375366169358</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-15.52420426165046</v>
+        <v>-13.30789410922967</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-22.89723351670249</v>
+        <v>-23.96401308615049</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-23.31738437001596</v>
+        <v>-20.78774244128574</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-19.38794501608567</v>
+        <v>-20.53869757927038</v>
       </c>
     </row>
     <row r="31">
@@ -1875,150 +1875,150 @@
         <v>17</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-11.30444544229906</v>
+        <v>-11.33364123665169</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-12.91563153536281</v>
+        <v>-12.91681832180746</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.545697037764903</v>
+        <v>-1.545850427769224</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.34923398817632</v>
+        <v>10.34873949579831</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.810944435080792</v>
+        <v>9.859490354846564</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.10831846471571</v>
+        <v>10.13227587366532</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15.90596104662593</v>
+        <v>15.95397272561625</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.208166420690056</v>
+        <v>-2.158918858296339</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>15.37791024631642</v>
+        <v>15.45116735609611</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.64563850881008</v>
+        <v>8.744985834104654</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.440937350549973</v>
+        <v>8.540845386568648</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.59296256172891</v>
+        <v>2.716659182757155</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.709541232761048</v>
+        <v>-3.56085168498322</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.483805582534515</v>
+        <v>-3.311806822967853</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 118.3</t>
+          <t>X ≈ 118.2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>16</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>16.26908396946565</v>
+        <v>16.23988817511302</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.65789787640173</v>
+        <v>14.65671108995708</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.013126491646695</v>
+        <v>8.012973101642373</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.894937917860595</v>
+        <v>-4.846391998094823</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-10.84756388822542</v>
+        <v>-10.82360647927581</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-4.682274247491549</v>
+        <v>-4.634262568501228</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.149342891278458</v>
+        <v>-5.100095328884741</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.53967495219894</v>
+        <v>13.61293206197863</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1897561558690768</v>
+        <v>0.2891034811636501</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.235054997608799</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.269433149964037</v>
+        <v>6.393129770992282</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>12.09928229665071</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>12.32501794687725</v>
+        <v>12.49701670644391</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 122.5</t>
+          <t>X ≈ 122.3</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>7</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.661941112322687</v>
+        <v>4.632745317970056</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-25.52067355216961</v>
+        <v>-25.52186033861427</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-11.499505507622</v>
+        <v>-11.50000000000001</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-12.0377950607177</v>
+        <v>-11.98924914095193</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-11.74042103108261</v>
+        <v>-11.716463622133</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-26.11084567606306</v>
+        <v>-26.06283399707274</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-12.29220003413562</v>
+        <v>-12.2429524717419</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-12.35318219065839</v>
+        <v>-12.2799250808787</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.08261329872623</v>
+        <v>1.181960624020803</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-27.69351643096263</v>
+        <v>-27.59360839494396</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-13.37342399289312</v>
+        <v>-13.24972737186488</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-13.79357484620653</v>
+        <v>-13.6448852984287</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.56783919598</v>
+        <v>-13.39584043641334</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>17</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4602604400539647</v>
+        <v>0.4310646457013334</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>4.730240501721873</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>21.9837147269409</v>
+        <v>21.98356133693657</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>16.23158692935279</v>
+        <v>16.23109243697479</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.928591493904108</v>
+        <v>3.97713741366988</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.656387417637276</v>
+        <v>-1.632430008687663</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.741097776903352</v>
+        <v>-1.693086097913032</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.090519361866562</v>
+        <v>-8.041271799472845</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-19.91620740074229</v>
+        <v>-19.84295029096259</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-9.001420314719283</v>
+        <v>-8.90207298942471</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.558584409373509</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.592962561728875</v>
+        <v>2.71665918275712</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-9.591894173937476</v>
+        <v>-9.443204626159648</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-9.366158523710943</v>
+        <v>-9.194159764144281</v>
       </c>
     </row>
   </sheetData>
@@ -2214,101 +2214,101 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2009843065645853</v>
+        <v>-0.1998005408402861</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.09210212359818115</v>
+        <v>-0.09182941113746068</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1077566505830276</v>
+        <v>-0.1074648545619254</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1350768664730069</v>
+        <v>-0.134704307617433</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1719698924761204</v>
+        <v>-0.1725847926420059</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2030326382254657</v>
+        <v>-0.2030196762566163</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2256197908371789</v>
+        <v>-0.2260794218866025</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2397190515128642</v>
+        <v>-0.2401684104924442</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2872857123503749</v>
+        <v>-0.288140062777785</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3173308431534991</v>
+        <v>-0.3186835039692681</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.337298950081248</v>
+        <v>-0.3386108327791604</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3625961898891745</v>
+        <v>-0.3643684001853913</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4022461944228937</v>
+        <v>-0.4044671799616992</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4073695286609222</v>
+        <v>-0.4100947841635616</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 14.17</t>
+          <t>X &gt; 14.16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3956</v>
+        <v>3967</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.25113522932498</v>
+        <v>-0.2488052922236648</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3622634139207577</v>
+        <v>-0.3611954192159956</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2645392507278146</v>
+        <v>-0.2637991457180249</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3727855306751025</v>
+        <v>-0.371726714321639</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3930463667886741</v>
+        <v>-0.3946817365253636</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3846476420095186</v>
+        <v>-0.3849272339928334</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.430444825336707</v>
+        <v>-0.4319475206905423</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4295044258568694</v>
+        <v>-0.4310794718496709</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5019180798637635</v>
+        <v>-0.5046409490989987</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5551933390805033</v>
+        <v>-0.5592344689749353</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6700978187589683</v>
+        <v>-0.6738530872793262</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.7479998970293025</v>
+        <v>-0.7528767797760878</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.8003259924571964</v>
+        <v>-0.8064636394424198</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.8132530339114368</v>
+        <v>-0.8206666815066868</v>
       </c>
     </row>
     <row r="8">
@@ -2318,1453 +2318,1453 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3716</v>
+        <v>3727</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2148929680511174</v>
+        <v>-0.2106465842452749</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3635613510659965</v>
+        <v>-0.3623448073415787</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3414482333330966</v>
+        <v>-0.3404244371483358</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.8676521221454223</v>
+        <v>-0.8650368897893728</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.9352063742363939</v>
+        <v>-0.9384690858892171</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.8381653919848588</v>
+        <v>-0.8386667202397007</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.8009957086788546</v>
+        <v>-0.8045892958714305</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9043133372751484</v>
+        <v>-0.9077567272237914</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9507174154442524</v>
+        <v>-0.9570036293397806</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.9795986828406882</v>
+        <v>-0.989039107954639</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.9812665942169616</v>
+        <v>-0.9907742317880803</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.9589154245382971</v>
+        <v>-0.9714451820781562</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8530313971884027</v>
+        <v>-0.8689809452710335</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.908297446018338</v>
+        <v>-0.9269838301807312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 22.34</t>
+          <t>X &gt; 22.33</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3392</v>
+        <v>3403</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4398000246606415</v>
+        <v>-0.4316574923342884</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7431009485100546</v>
+        <v>-0.7404338587983261</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6814077428521941</v>
+        <v>-0.6791768690663957</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.123256242483848</v>
+        <v>-1.119521995730615</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.410668585311299</v>
+        <v>-1.417318141119395</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.362269770578408</v>
+        <v>-1.363404192556423</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.460738501684041</v>
+        <v>-1.467107143281375</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.558995628182437</v>
+        <v>-1.565334401926606</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.574764258869735</v>
+        <v>-1.58659845445338</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.672729120927244</v>
+        <v>-1.690277205657686</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.68467990666219</v>
+        <v>-1.7023241067131</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.634220356223267</v>
+        <v>-1.65753102195918</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.3898865804492</v>
+        <v>-1.419771986358761</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.383708468217094</v>
+        <v>-1.419013267108838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 26.42</t>
+          <t>X &gt; 26.41</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3107</v>
+        <v>3118</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2176736549324261</v>
+        <v>-0.2053743088818649</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4484424125227378</v>
+        <v>-0.4269424483073223</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3937755950305899</v>
+        <v>-0.4191217093761139</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.8413995686171845</v>
+        <v>-0.8486519888314206</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.009260332761009</v>
+        <v>-1.032289433992219</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.080056660470888</v>
+        <v>-1.112068017737393</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9399035439901908</v>
+        <v>-0.9483651326038824</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9719649992475183</v>
+        <v>-0.9654799442692763</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.097214507955393</v>
+        <v>-1.066555117508635</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.383291095818571</v>
+        <v>-1.345511903451822</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.15240480946516</v>
+        <v>-1.147403109367069</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.035970516809755</v>
+        <v>-1.039519363067932</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.9235619761935538</v>
+        <v>-0.8894559939293742</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.130485754442361</v>
+        <v>-1.121488745769049</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 30.51</t>
+          <t>X &gt; 30.49</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2799</v>
+        <v>2802</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.5180323760018766</v>
+        <v>-0.5472281703545079</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2734011956895444</v>
+        <v>-0.2745879821342001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1685294683817773</v>
+        <v>-0.1686828583860986</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6093250242937742</v>
+        <v>-0.6098195166717773</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5765938778891098</v>
+        <v>-0.5280479581233379</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.7788629603168289</v>
+        <v>-0.7549055513672158</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6851293509891292</v>
+        <v>-0.6371176719988085</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5811772952755163</v>
+        <v>-0.5319297328817996</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.6064706580795232</v>
+        <v>-0.5332135482998268</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.028123929784108</v>
+        <v>-0.9287766044895349</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8759371508565792</v>
+        <v>-0.7760291148379039</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.9288888778830682</v>
+        <v>-0.8249287586293264</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.8292891319207172</v>
+        <v>-0.7204435731303462</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.012334679060594</v>
+        <v>-0.9353530294590158</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 34.6</t>
+          <t>X &gt; 34.57</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8316803105021719</v>
+        <v>-0.8414347038576366</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2304770230350357</v>
+        <v>-0.2131119900589269</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1792568214939223</v>
+        <v>0.1571226794470348</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3094819650822842</v>
+        <v>0.2870067206617151</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5354723798063787</v>
+        <v>0.561730237530476</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.01188408130672514</v>
+        <v>-0.009875075978705183</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3781712708222926</v>
+        <v>-0.3519947759802022</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4429872999670366</v>
+        <v>-0.4157366638263511</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.38329367209721</v>
+        <v>-0.3320820112019902</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.7505093308566728</v>
+        <v>-0.6734015449723429</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.351831567153873</v>
+        <v>-0.2744056837026463</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2547117192511621</v>
+        <v>-0.176029859084025</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3705244666343148</v>
+        <v>-0.2897241748718216</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.9275998541698698</v>
+        <v>-0.8850701451845637</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 38.68</t>
+          <t>X &gt; 38.66</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5803998409519977</v>
+        <v>-0.5644953223084528</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1547303494191752</v>
+        <v>0.1495615353392594</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.698485478038144</v>
+        <v>0.6934700542913106</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.063342249970013</v>
+        <v>1.057765722322678</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.69821083859182</v>
+        <v>1.740574715454208</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.338616308865099</v>
+        <v>1.310125353823075</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5969373902371302</v>
+        <v>0.5931167095108734</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3645003747938986</v>
+        <v>0.3616955759442249</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4912235209459226</v>
+        <v>0.5122522682607737</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1105679813030562</v>
+        <v>0.1572469410791797</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6566880337420642</v>
+        <v>0.7032236993564922</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5502872090912945</v>
+        <v>0.6207434606313811</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.03628370444048556</v>
+        <v>0.1318208833408718</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4625407385687623</v>
+        <v>-0.4161337858205059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 42.77</t>
+          <t>X &gt; 42.74</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7420182242208213</v>
+        <v>-0.7196254539623439</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4805451412546802</v>
+        <v>-0.4321451366596207</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2482789796082585</v>
+        <v>0.2430639621448591</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5925223147428937</v>
+        <v>0.640184775139339</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.017314623605472</v>
+        <v>1.112988012594691</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5121204349420054</v>
+        <v>0.5840632160742203</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.266896432016118</v>
+        <v>0.363065063780887</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.06735052766223504</v>
+        <v>0.1644690751773439</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4344047542320268</v>
+        <v>0.5550753008882197</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1479913026649839</v>
+        <v>-0.001516508146963247</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8244075925793766</v>
+        <v>0.9701848401480504</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6447675533884123</v>
+        <v>0.8145621600891033</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.2781212479615718</v>
+        <v>0.4728515878812445</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.4292647083690042</v>
+        <v>-0.2401559285106671</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 46.85</t>
+          <t>X &gt; 46.82</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8819000403744539</v>
+        <v>-0.8813472274684173</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5250664532414788</v>
+        <v>-0.4977142327226147</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1256726171080373</v>
+        <v>0.1534156339104342</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2558977606963992</v>
+        <v>0.2832996751251144</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6401174326929535</v>
+        <v>0.7159927591271043</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6299883872972885</v>
+        <v>0.6814642029614006</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1927293520426829</v>
+        <v>-0.1167456662271888</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1062924607740712</v>
+        <v>-0.02941309163818318</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6937339927892552</v>
+        <v>0.7940937091819862</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.08981765648400142</v>
+        <v>0.2161163883547133</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.176629413352956</v>
+        <v>1.302695055754093</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.8420038756713808</v>
+        <v>0.9920849031374246</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7293560973887239</v>
+        <v>0.8427782365613012</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1288641007233977</v>
+        <v>0.2928065036166174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 50.94</t>
+          <t>X &gt; 50.9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.09419126560297997</v>
+        <v>0.1327453179701621</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4858664028681972</v>
+        <v>0.5495682328143019</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3772180510173087</v>
+        <v>0.4415445302138821</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6505047110577422</v>
+        <v>0.7142857142857082</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3983381908661983</v>
+        <v>0.5107508590480805</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4095891875971347</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3188979957033666</v>
+        <v>-0.3485482827870285</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6429051230380267</v>
+        <v>-0.6715239003132325</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4406048520557917</v>
+        <v>0.4343606334071168</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3775243962123369</v>
+        <v>0.3962463383064261</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.317315369568746</v>
+        <v>1.334963033627467</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7079166978897362</v>
+        <v>0.8217011995637975</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9315426686106605</v>
+        <v>1.14082898728568</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6565630112549243</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 55.03</t>
+          <t>X &gt; 54.98</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.128860274353805</v>
+        <v>0.05611334067593532</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.09182496836536558</v>
+        <v>0.04578393763928545</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3029464163896733</v>
+        <v>-0.3479540506754191</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.08987123137629283</v>
+        <v>-0.1352885525070988</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2003396297782274</v>
+        <v>0.2032768760774033</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0006134108631812296</v>
+        <v>-0.0206263468255159</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8297473212281687</v>
+        <v>-0.8263155486337581</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.131115882164863</v>
+        <v>-1.126585395109821</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.05065258268766826</v>
+        <v>0.07816385005801152</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2193159236670539</v>
+        <v>-0.1661945320814695</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5701834151730054</v>
+        <v>0.6230425038261487</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1074613189782099</v>
+        <v>0.1845204994691869</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1015606727899012</v>
+        <v>0.2032698576735754</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1615962401663964</v>
+        <v>0.2867518057816625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 59.11</t>
+          <t>X &gt; 59.06</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1041</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.06471317215537198</v>
+        <v>0.03551737780274067</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2016122100535114</v>
+        <v>-0.2027989964981671</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.308199156768211</v>
+        <v>-0.3083525467725323</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8787022596347569</v>
+        <v>0.8782077672567539</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.0522282684987232</v>
+        <v>0.100774188264495</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3228280572936697</v>
+        <v>-0.2988706483440566</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.464214689374444</v>
+        <v>-1.416203010384123</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.411590729895082</v>
+        <v>-2.362343167501365</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.223773654909699</v>
+        <v>-1.150516545130003</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.01701617842496</v>
+        <v>-0.9176688531303867</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2611025432173335</v>
+        <v>-0.1611945071986582</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9952162256362627</v>
+        <v>-0.871519604608018</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.511428558296444</v>
+        <v>-1.362739010518617</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.093569949376352</v>
+        <v>-0.9215711898096899</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 63.2</t>
+          <t>X &gt; 63.15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.08440186931431271</v>
+        <v>-0.2324545580757018</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.150925653009942</v>
+        <v>-1.056412554294461</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4563724190285967</v>
+        <v>-0.3655518441276016</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5453124195488712</v>
+        <v>0.6320111558723198</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4287069810413797</v>
+        <v>-0.2910774644722238</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.329590032016313</v>
+        <v>-1.211350513983014</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.503625010018872</v>
+        <v>-2.356605301690031</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.624288425047439</v>
+        <v>-3.473197281162307</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.704878424707474</v>
+        <v>-2.425571191817554</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.119067373542769</v>
+        <v>-2.815560293239905</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.125511451192942</v>
+        <v>-1.826642172446277</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.18045791757401</v>
+        <v>-2.853074133562949</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.491676309013769</v>
+        <v>-3.13977219027862</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.048075735039973</v>
+        <v>-2.673807588566937</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 67.28</t>
+          <t>X &gt; 67.23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5829692367407517</v>
+        <v>0.7366414218662598</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8978387598432889</v>
+        <v>-0.7166655334194587</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5326832061187545</v>
+        <v>0.5779081665775223</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.140092182823153</v>
+        <v>3.175324675324674</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.819534050848702</v>
+        <v>1.776984625281841</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.03085853680713058</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.09687659429737</v>
+        <v>-0.997898932137673</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.389238588801192</v>
+        <v>-3.281913510702836</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.407195973485635</v>
+        <v>-2.409795210748733</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.60522428741654</v>
+        <v>-2.584273142213057</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.636522577358605</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.557815872200152</v>
+        <v>-3.379597501734914</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.977966725513561</v>
+        <v>-3.774755428298739</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.230718689367862</v>
+        <v>-3.006230046802848</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 71.37</t>
+          <t>X &gt; 71.31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1425407595891031</v>
+        <v>0.2591189443437827</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.931608296437687</v>
+        <v>-1.785596602350523</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.400453755266795</v>
+        <v>-1.256257667588315</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.198907190790699</v>
+        <v>1.335164835164832</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8149386253493276</v>
+        <v>0.999761848059066</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.048181172176079</v>
+        <v>-0.8812987869681592</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.595854494405209</v>
+        <v>-1.403493337732087</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.451812027080848</v>
+        <v>-3.253941482730816</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.586868257677693</v>
+        <v>-2.367837168790686</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.665182115735945</v>
+        <v>-2.422434980374902</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.789636360415898</v>
+        <v>-1.549652350987913</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.761431047566745</v>
+        <v>-3.645331767469173</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.644544863843116</v>
+        <v>-4.502028155571459</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.264488225962261</v>
+        <v>-3.945290985863778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 75.45</t>
+          <t>X &gt; 75.39</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4236709500334612</v>
+        <v>-0.3672546820298379</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.644874932184948</v>
+        <v>-3.736146052899983</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.787410180982924</v>
+        <v>-2.70131261264325</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1527127654804232</v>
+        <v>-0.2500000000000071</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5121114420108199</v>
+        <v>-0.3821062838090725</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.361427931159277</v>
+        <v>-2.252177907847276</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.088356537294857</v>
+        <v>-1.955691139929883</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.344333946734544</v>
+        <v>-4.385809614598948</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.868643473561434</v>
+        <v>-3.708496509450029</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.82410788706482</v>
+        <v>-3.818039375979289</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.134354662498531</v>
+        <v>-3.129322680658241</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.246667028926751</v>
+        <v>-5.214013086150494</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.024599635370755</v>
+        <v>-5.966313869857174</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.798863985144223</v>
+        <v>-5.717269007841807</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 79.54</t>
+          <t>X &gt; 79.47</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6663999015020892</v>
+        <v>-0.5986430120097239</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.293715026823989</v>
+        <v>-4.193892531773223</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.873970282546772</v>
+        <v>-2.776765328941046</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7276161067003457</v>
+        <v>-0.6348088531187202</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.26590565979604</v>
+        <v>-1.12405799407064</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.581434855967402</v>
+        <v>-2.460930422937828</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.069371021685185</v>
+        <v>-2.924000999084818</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.955794504181597</v>
+        <v>-5.804320680997328</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.613550854252765</v>
+        <v>-5.438878803212603</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.253792231227784</v>
+        <v>-5.055463923262991</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-4.047203066907329</v>
+        <v>-3.851153666573737</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.006266607277254</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.40142453384108</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.223369149896939</v>
+        <v>-5.951172428364949</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 83.63</t>
+          <t>X &gt; 83.56</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.683649515727971</v>
+        <v>-1.828293643068797</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.661578205602737</v>
+        <v>-4.775107091861024</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.550654829537727</v>
+        <v>-2.668845080175721</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.08526507487067647</v>
+        <v>-0.03896103896104108</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.136395776630479</v>
+        <v>-1.21002836173114</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.750183478202686</v>
+        <v>-1.846333752003133</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.518265135874316</v>
+        <v>-2.588808023046766</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.718818973282929</v>
+        <v>-5.781913510702843</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5.779801129805705</v>
+        <v>-5.591613392566906</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.490767762126445</v>
+        <v>-5.279078337018248</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.961983726764778</v>
+        <v>-2.755946057281619</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-5.205509902427671</v>
+        <v>-4.970506592644</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-6.081241621344724</v>
+        <v>-5.820209973753272</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.311086836721834</v>
+        <v>-6.025710566283358</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 87.71</t>
+          <t>X &gt; 87.64</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.699666030534353</v>
+        <v>-1.860761175536339</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.571268790264845</v>
+        <v>-3.703678520432454</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.101456841686556</v>
+        <v>-1.240273651604298</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.112101635235142</v>
+        <v>0.9675324675324575</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.05297874880611175</v>
+        <v>-0.04119719289997903</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.17048055489213</v>
+        <v>-0.2878921935615679</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.036440914158298</v>
+        <v>-1.127769062007815</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.368092891278373</v>
+        <v>-4.191004419793749</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.908241714467813</v>
+        <v>-3.708496509450029</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.976910510797673</v>
+        <v>-3.753104311044233</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.577445002391201</v>
+        <v>-1.359842161177724</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.668066850035878</v>
+        <v>-4.418558540695948</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.348634370015951</v>
+        <v>-5.073456727000035</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.38331538645609</v>
+        <v>-5.08415212472493</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 91.8</t>
+          <t>X &gt; 91.72</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.631066180684506</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.542552574048635</v>
+        <v>-4.392690107647631</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1325191539988708</v>
+        <v>-0.2954101318904776</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.799507791391299</v>
+        <v>1.630881094952947</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0600170370944042</v>
+        <v>0.243428361186659</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6576913670297841</v>
+        <v>0.8156150776103743</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.9285204937378779</v>
+        <v>-0.7420469996390366</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-3.797991539927025</v>
+        <v>-3.603089340860706</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.558673396149494</v>
+        <v>-3.340660752392708</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.507691291578453</v>
+        <v>-3.266285740393315</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.610290347736544</v>
+        <v>-1.374617804695873</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.578915198384223</v>
+        <v>-4.609864240983683</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.698765751397339</v>
+        <v>-4.705620969942714</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-4.473030101170806</v>
+        <v>-4.456576107927347</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 95.88</t>
+          <t>X &gt; 95.8</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.022432276021718</v>
+        <v>-2.869824055102811</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.467553387136086</v>
+        <v>-2.294727758963703</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.191826852657606</v>
+        <v>2.347505475743176</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.571149469170159</v>
+        <v>5.714799588900306</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.866794934125004</v>
+        <v>2.707564836437591</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.16416896376009</v>
+        <v>3.340062585472346</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.996426113519192</v>
+        <v>2.200269805599405</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9977183425419085</v>
+        <v>-0.7835485662947335</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.058700499064685</v>
+        <v>-0.82052117543153</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.8255868044198209</v>
+        <v>-0.5652130655990248</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.496787849594355</v>
+        <v>1.748632098375673</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.078942301299413</v>
+        <v>-1.790323466417711</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.221114815262638</v>
+        <v>-2.904905853413183</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.27335750438629</v>
+        <v>-1.936436530966169</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 99.97</t>
+          <t>X &gt; 99.88</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.697366246984565</v>
+        <v>-2.941146307645603</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.27824930974537</v>
+        <v>-1.507082013491114</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.223083201603494</v>
+        <v>1.978490343021775</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.517810509694023</v>
+        <v>4.263546798029545</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.050159726043155</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.679492388830816</v>
+        <v>1.460876279344831</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7289811637637769</v>
+        <v>0.5381512246021316</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.335490077425561</v>
+        <v>-2.513888432332934</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-0.8267231104352462</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6489884328755977</v>
+        <v>-0.7884827257329903</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.743713006266809</v>
+        <v>1.593583723282649</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.118012737481763</v>
+        <v>-2.227559884180039</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.971064023695604</v>
+        <v>-3.053752293502498</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.312427940568639</v>
+        <v>-2.373672948728498</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 104.1</t>
+          <t>X &gt; 104</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.313376763518647</v>
+        <v>-4.593445158220312</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.78320160003797</v>
+        <v>-3.051622243376173</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.010508690599664</v>
+        <v>0.7213064349757943</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.282095090732518</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.173124909364574</v>
+        <v>1.924441335238555</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.423378520151495</v>
+        <v>1.155560187390812</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.8151079514612505</v>
+        <v>0.5740707648320225</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.840442367718161</v>
+        <v>-4.058428662217992</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2365030582723548</v>
+        <v>-0.4495679380214526</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5628616451781241</v>
+        <v>-0.7525631855030994</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2795576154098498</v>
+        <v>0.08496303362747426</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.398106117051583</v>
+        <v>-4.544370229007633</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.341817179789075</v>
+        <v>-5.460361488904795</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.116081529562543</v>
+        <v>-5.211316626889428</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 108.1</t>
+          <t>X &gt; 108</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-5.457106506724827</v>
+        <v>-5.764549694709466</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.687340218836276</v>
+        <v>-4.980862874539881</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>-0.6408730522036947</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.190970682854186</v>
+        <v>1.855874894336424</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7282712511938882</v>
+        <v>-0.4085221756095763</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-0.7274526331220059</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.3953232303152561</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.554104796040278</v>
+        <v>-4.804237340718977</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1468178093417123</v>
+        <v>0.4842338371264745</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7031009869881473</v>
+        <v>-0.3395947436885081</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.473150235704033</v>
+        <v>1.823128714100847</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.849614469083491</v>
+        <v>-4.035864311847867</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.460241512873097</v>
+        <v>-5.022738214743057</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.639267767408462</v>
+        <v>-4.77369335272769</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 112.2</t>
+          <t>X &gt; 112.1</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>141</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.253965675924427</v>
+        <v>-4.283161470277058</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.02827233636414</v>
+        <v>-3.029459122808795</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8322754278169953</v>
+        <v>0.8321220378126739</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.217819720341524</v>
+        <v>5.217325227963521</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.842650734621721</v>
+        <v>1.891196654387493</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.430804906100775</v>
+        <v>1.454762315050388</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.47375412130269</v>
+        <v>3.521765800293011</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.667073387732273</v>
+        <v>-2.617825825338556</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.945703320993175</v>
+        <v>3.018960430772871</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>2.095784524663316</v>
+        <v>2.195131849957889</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.727962799027239</v>
+        <v>4.827870835045914</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.202198055709637</v>
+        <v>-0.07850143468139237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.040788625335104</v>
+        <v>-1.892099077557276</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.815052975108571</v>
+        <v>-1.643054215541909</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 116.3</t>
+          <t>X &gt; 116.2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.287367643437577</v>
+        <v>-3.316563437790208</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.672747284888509</v>
+        <v>-1.673934071333164</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.158287781969356</v>
+        <v>1.158134391965035</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.514319377170629</v>
+        <v>4.513824884792626</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.750223372462024</v>
+        <v>0.7987692922277958</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2411457891938866</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.769338655734181</v>
+        <v>1.817350334724502</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.7299880525687</v>
+        <v>-2.680740490174983</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.241287855424666</v>
+        <v>1.314544965204362</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.197820671998031</v>
+        <v>1.297167997292604</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.218925965350735</v>
+        <v>4.31883400136941</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5854055597133012</v>
+        <v>-0.4617089386850566</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.812008025929934</v>
+        <v>-1.663318478152107</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.586272375703402</v>
+        <v>-1.41427361613674</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 120.4</t>
+          <t>X &gt; 120.3</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>108</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-6.184619734238055</v>
+        <v>-6.213815528590686</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1427561212764061</v>
+        <v>0.1426027312720848</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.586543563620921</v>
+        <v>1.635089483386693</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.883917593256008</v>
+        <v>1.907875002205621</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.725133159915771</v>
+        <v>2.773144838906092</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.371565113500594</v>
+        <v>-2.322317551106877</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5806954181715227</v>
+        <v>-0.5074383083918264</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.347163563276396</v>
+        <v>1.44651088857097</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.920240182793982</v>
+        <v>4.020148218812658</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.600937220406252</v>
+        <v>-1.477240599378007</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.872939925571508</v>
+        <v>-3.72425037779368</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.647204275344976</v>
+        <v>-3.475205515778313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 124.5</t>
+          <t>X &gt; 124.4</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>101</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.936361575088803</v>
+        <v>-6.965557369441434</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.606953608746693</v>
+        <v>-2.608140395191349</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03142796379876245</v>
+        <v>-0.0315813538030838</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.049292229294544</v>
+        <v>5.048797736916541</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.530804656396867</v>
+        <v>2.579350576162639</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.828178686031954</v>
+        <v>2.852136094981567</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.723666346567768</v>
+        <v>4.771678025558089</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.683996356624903</v>
+        <v>-1.634748794231186</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2352195066543032</v>
+        <v>0.3084766164339996</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.365498730126411</v>
+        <v>1.464846055420985</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.111292621371177</v>
+        <v>6.211200657389853</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.7850222955804256</v>
+        <v>-0.6613256745521809</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.185371168695816</v>
+        <v>-3.036681620917989</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.959635518469284</v>
+        <v>-2.787636758902622</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 128.6</t>
+          <t>X &gt; 128.5</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-8.433296982915309</v>
+        <v>-8.46249277726794</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>6.032011466794074</v>
+        <v>6.080023145784395</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3874381293736064</v>
+        <v>-0.3381905669798897</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>3.463565679678517</v>
+        <v>3.56291300497309</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>6.830293092846894</v>
+        <v>6.930201128865569</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.468662088131111</v>
+        <v>-1.344965467102867</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.88881294144452</v>
+        <v>-1.740123393666693</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.663077291217988</v>
+        <v>-1.491078531651326</v>
       </c>
     </row>
   </sheetData>
@@ -3911,98 +3911,98 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.036936015456305</v>
+        <v>5.036782625451984</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.548113539997047</v>
+        <v>7.547619047619044</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.390776367853739</v>
+        <v>9.439322287619511</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.36534480012742</v>
+        <v>14.41335647911774</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15.08875234681685</v>
+        <v>15.13799990921057</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.59919876172266</v>
+        <v>18.67245587150236</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.13023234634518</v>
+        <v>20.22957967163975</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.11600737856118</v>
+        <v>21.21591541457985</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>22.34086172139269</v>
+        <v>22.46455834242094</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>24.30166324903166</v>
+        <v>24.45035279680949</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>24.52739889925819</v>
+        <v>24.69939765882486</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 14.17</t>
+          <t>X &lt; 14.16</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>216</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.46352841391009</v>
+        <v>4.434332619557459</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.481971950475888</v>
+        <v>7.480785164031232</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.772385750906032</v>
+        <v>4.772232360901711</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.217425709309211</v>
+        <v>7.216931216931208</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.605062082139447</v>
+        <v>7.653608001905219</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.206614641397252</v>
+        <v>9.254626320387572</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.202508960573475</v>
+        <v>9.251756522967192</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.99337865590256</v>
+        <v>11.06663576568226</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.99531171142455</v>
+        <v>12.09465903671912</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.10542536797917</v>
+        <v>14.20533340399784</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>15.52869240922337</v>
+        <v>15.65238903025162</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>16.49743044479887</v>
+        <v>16.64611999257669</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>16.7231660950254</v>
+        <v>16.89516485459206</v>
       </c>
     </row>
     <row r="8">
@@ -4015,1450 +4015,1450 @@
         <v>456</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.364038227279011</v>
+        <v>3.362851440834355</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.74996859690993</v>
+        <v>2.749815206905609</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.266158652778998</v>
+        <v>7.265664160400995</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.824360327753475</v>
+        <v>7.872906247519246</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.244541374932432</v>
+        <v>7.268498783882045</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.159831015666263</v>
+        <v>7.207842694656584</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8.00855184556373</v>
+        <v>8.057799407957447</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.605464425883063</v>
+        <v>8.67872153566276</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.852036857623375</v>
+        <v>8.951384182917948</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.866633944977224</v>
+        <v>8.966541980995899</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.681713851718506</v>
+        <v>8.80541047274675</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.822966507177028</v>
+        <v>7.971656054954856</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.268000403017588</v>
+        <v>8.43999916258425</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 22.34</t>
+          <t>X &lt; 22.33</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>780</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.878058328440005</v>
+        <v>1.848862534087374</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.472000440504381</v>
+        <v>3.470813654059725</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.949023927544211</v>
+        <v>2.948870537539889</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.0023259942095</v>
+        <v>5.001831501831496</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.258908235985608</v>
+        <v>6.30745415575138</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.171666881005301</v>
+        <v>6.195624289954914</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.727982162764782</v>
+        <v>6.775993841755103</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.158349416413934</v>
+        <v>7.207596978807651</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.353777516301413</v>
+        <v>7.42703462608111</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.785910002022831</v>
+        <v>7.885257327317404</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.837619100172901</v>
+        <v>7.937527136191576</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.615586996117962</v>
+        <v>7.739283617146206</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.554410501778918</v>
+        <v>6.703100049556745</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.523735895595195</v>
+        <v>6.695734655161857</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 26.42</t>
+          <t>X &lt; 26.41</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1065</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6031961189983619</v>
+        <v>0.5682463840682388</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.473847361902287</v>
+        <v>1.410442433240746</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.131104019736668</v>
+        <v>1.203271609105144</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.531823987625017</v>
+        <v>2.545842217484008</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.024462269580873</v>
+        <v>3.082712479517156</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.32183629921596</v>
+        <v>3.409586798035079</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.010033444816052</v>
+        <v>3.02928883336785</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.105816583393299</v>
+        <v>3.085124502733684</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.56901767520354</v>
+        <v>3.477164271716376</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.409239723944111</v>
+        <v>4.301521475540326</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.722498178894575</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.393846295504027</v>
+        <v>3.405782067149822</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.067592155805642</v>
+        <v>2.972643514222163</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.66891466049227</v>
+        <v>3.653119992828891</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 30.51</t>
+          <t>X &lt; 30.49</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.02595309455603</v>
+        <v>1.076688749001107</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6835852859531926</v>
+        <v>0.680580436690839</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3284776864331675</v>
+        <v>0.3261914924470517</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.295525548278619</v>
+        <v>1.286279141419321</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.232690798600657</v>
+        <v>1.124831023487957</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.715933934706328</v>
+        <v>1.653895320580162</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.599497720554844</v>
+        <v>1.489656739856038</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.39135478314023</v>
+        <v>1.280582392816854</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.516947679471578</v>
+        <v>1.356438555485042</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.382259794879182</v>
+        <v>2.161847163474036</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.07445776527085</v>
+        <v>1.855194247500307</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.181669129570821</v>
+        <v>1.955313429705306</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.980017912091355</v>
+        <v>1.746886460926369</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.351419986207176</v>
+        <v>2.182932709340356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 34.6</t>
+          <t>X &lt; 34.57</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.197718460342635</v>
+        <v>1.20551134655831</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4426446372969863</v>
+        <v>0.4149078112686411</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2735558890249905</v>
+        <v>-0.2398095579943345</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4061766666516462</v>
+        <v>-0.3712108524535296</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.7356458824623218</v>
+        <v>-0.7701456637839286</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1249862888701614</v>
+        <v>0.1212292014753231</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7223329586513074</v>
+        <v>0.6798889288562862</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8199242482015308</v>
+        <v>0.7753453291647006</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7920404164212087</v>
+        <v>0.7124323559232906</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.336205860011006</v>
+        <v>1.215574069398862</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7510407880173275</v>
+        <v>0.6330795727681462</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.607799046944578</v>
+        <v>0.489125059567165</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7797145050580596</v>
+        <v>0.6576654213289572</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.597516466711468</v>
+        <v>1.530035574368441</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 38.68</t>
+          <t>X &lt; 38.66</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2042</v>
+        <v>2050</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.586269948044027</v>
+        <v>0.5679298619768005</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.07359262530300725</v>
+        <v>-0.06807067531926947</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7344368611797378</v>
+        <v>-0.7267163694880594</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.065570841605421</v>
+        <v>-1.05617198335645</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.724206210543478</v>
+        <v>-1.762370628497891</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.30327399071448</v>
+        <v>-1.269427664892959</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4830554974916339</v>
+        <v>-0.4777239199840508</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2397190515128642</v>
+        <v>-0.2362820993126675</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3227395150543302</v>
+        <v>-0.3438805900895829</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.07667547127241647</v>
+        <v>0.02741896314994108</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4919508732326889</v>
+        <v>-0.5391236687592738</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3813255382394942</v>
+        <v>-0.453848786512502</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1563342065429723</v>
+        <v>0.05574853872401064</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6758994356137791</v>
+        <v>0.6250654869317103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 42.77</t>
+          <t>X &lt; 42.74</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2304</v>
+        <v>2312</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.584714366702265</v>
+        <v>0.5651569923173199</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4651332975681228</v>
+        <v>0.4247833791137907</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2085675446539952</v>
+        <v>-0.2037724859597745</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4439808334202837</v>
+        <v>-0.4811738648948065</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7859413780681663</v>
+        <v>-0.8610408563455323</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3353397428338667</v>
+        <v>-0.3925719965172334</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.09352965874704466</v>
+        <v>-0.1711319087341678</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.06936650672941624</v>
+        <v>-0.009499988073613963</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1843285140056565</v>
+        <v>-0.2816514511850272</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2899945607237839</v>
+        <v>0.1703642756367927</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4973821229462771</v>
+        <v>-0.614281026847685</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3520419042658105</v>
+        <v>-0.4888927009177451</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.05349548112706515</v>
+        <v>-0.2114963786583601</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5194623913216887</v>
+        <v>0.3646637652674372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 46.85</t>
+          <t>X &lt; 46.82</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2547</v>
+        <v>2556</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5476107377345087</v>
+        <v>0.5455518574797011</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4035976418435681</v>
+        <v>0.3849042363746022</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.08718637499381288</v>
+        <v>-0.1044791772823572</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.131296252088795</v>
+        <v>-0.1482574323572052</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3743899726550737</v>
+        <v>-0.4214407310382526</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3297486963695491</v>
+        <v>-0.3614379925363878</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2335111030763244</v>
+        <v>0.1843094174526456</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1798107137372966</v>
+        <v>0.1301935079615504</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2906856906862885</v>
+        <v>-0.3537801598098227</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.09661890096703019</v>
+        <v>0.01566598116357198</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5960552417007392</v>
+        <v>-0.6746110187367336</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3828431451693177</v>
+        <v>-0.4774722618457901</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3099246134395841</v>
+        <v>-0.3815744989425909</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.07285854365777311</v>
+        <v>-0.03232601656079481</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 50.94</t>
+          <t>X &lt; 50.9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2774</v>
+        <v>2783</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.05895693473241437</v>
+        <v>-0.07806604520171589</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1796828845457838</v>
+        <v>-0.2113568885759349</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.196029702249092</v>
+        <v>-0.2279001982859583</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.297740318787838</v>
+        <v>-0.3292158968850742</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.1698211374078014</v>
+        <v>-0.2260481585532261</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1403388702527906</v>
+        <v>-0.148669180816519</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2619904055108861</v>
+        <v>0.2761316967316603</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4261966770669474</v>
+        <v>0.4395246065760787</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.08258125506995384</v>
+        <v>-0.07967912883924555</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.04872476565728334</v>
+        <v>-0.05849250017837448</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5213367920923204</v>
+        <v>-0.5297175119575925</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2147167059436583</v>
+        <v>-0.2720407855605913</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3263933790249638</v>
+        <v>-0.4316258567208848</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1885004381263613</v>
+        <v>-0.3061633151155618</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 55.03</t>
+          <t>X &lt; 54.98</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2965</v>
+        <v>2975</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.06318601038660887</v>
+        <v>-0.03353886638631565</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.02277862883715187</v>
+        <v>0.04129428379713573</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1166211153026921</v>
+        <v>0.1345404157750849</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.0635197024620382</v>
+        <v>0.08171811438142385</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.05297423258818412</v>
+        <v>-0.05416679702239691</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.06103012455623968</v>
+        <v>0.06937038964804287</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4321268292243801</v>
+        <v>0.4294530585945964</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5558068899400723</v>
+        <v>0.552370286680592</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1095402720641729</v>
+        <v>0.09783139083760517</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2213324441815558</v>
+        <v>0.1988886439698732</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.09917680832112552</v>
+        <v>-0.1207119160031525</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.08894781123814255</v>
+        <v>0.05705318382407398</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.09237063110789734</v>
+        <v>0.05039119926725277</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.06742941399360092</v>
+        <v>0.01592426946911729</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 59.11</t>
+          <t>X &lt; 59.06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3131</v>
+        <v>3142</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0318066157760839</v>
+        <v>-0.02199772029109681</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1236153437896661</v>
+        <v>0.1235785598366803</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.09619460113118095</v>
+        <v>0.09590998714833177</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2655945602440113</v>
+        <v>-0.2645032632342321</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.009520680865563236</v>
+        <v>-0.006658580132224756</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.165099380331398</v>
+        <v>0.1565522508828749</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5758519475370463</v>
+        <v>0.5578619154618565</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8914604239909849</v>
+        <v>0.8719504144444485</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5294708705662003</v>
+        <v>0.5032244038914797</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4628821526791995</v>
+        <v>0.428168961138141</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2124002433011967</v>
+        <v>0.1783652593826446</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4563147331112631</v>
+        <v>0.4134860050890552</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6289757832407474</v>
+        <v>0.5771955160798328</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4897416773148038</v>
+        <v>0.4306576994419942</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 63.2</t>
+          <t>X &lt; 63.15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3254</v>
+        <v>3261</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.01372737319995565</v>
+        <v>0.05555708164936135</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3781979376388023</v>
+        <v>0.3521739680506499</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1226211317692929</v>
+        <v>0.09732517988206268</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1287071882942712</v>
+        <v>-0.1535353976503515</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1464350517992656</v>
+        <v>0.1077364422721843</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4300265470902858</v>
+        <v>0.3973326458388655</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7915068012664221</v>
+        <v>0.7512943470433626</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.108325820378063</v>
+        <v>1.067642657035151</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8805003587652891</v>
+        <v>0.8029198145811165</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.999301889447878</v>
+        <v>0.9150606021436545</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.7200104781123287</v>
+        <v>0.6364336218627642</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.017590398121371</v>
+        <v>0.926534613162147</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.106578763624597</v>
+        <v>1.008701458162442</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9812871540069352</v>
+        <v>0.8767315178514465</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 67.28</t>
+          <t>X &lt; 67.23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3405</v>
+        <v>3413</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1403660012774779</v>
+        <v>-0.1750271780685395</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2538153478680201</v>
+        <v>0.2132804330228524</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.125046810460951</v>
+        <v>-0.1353913843388455</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6816849679859374</v>
+        <v>-0.6907683318726257</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.384100190854106</v>
+        <v>-0.3753224481240096</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.04644431570069685</v>
+        <v>0.05954172300418037</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3294490819339231</v>
+        <v>0.3072578993349424</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8459664021839544</v>
+        <v>0.8226891110100425</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6547775914950336</v>
+        <v>0.6557933843893196</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.7012697962327366</v>
+        <v>0.6969905165747434</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.4838812886886146</v>
+        <v>0.4801620968593312</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9164833407477957</v>
+        <v>0.8770243537156475</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.012230035934337</v>
+        <v>0.9672161326534905</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.843740413837601</v>
+        <v>0.7936032871646788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 71.37</t>
+          <t>X &lt; 71.31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3524</v>
+        <v>3533</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.03534068419565273</v>
+        <v>-0.05664312776346492</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4045042112434416</v>
+        <v>0.3777971266285292</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2514574676015187</v>
+        <v>0.2251627178952873</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.197055835053483</v>
+        <v>-0.2222289423813564</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1256200576850617</v>
+        <v>-0.1597742679987917</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.243885715398541</v>
+        <v>0.2131769152454694</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.3729509011914587</v>
+        <v>0.337488843928071</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7146797716111521</v>
+        <v>0.6783731650401847</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5845176838508763</v>
+        <v>0.5441078675183988</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6007538882952872</v>
+        <v>0.5559256468406915</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4404703647763668</v>
+        <v>0.396049006478151</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8028988334581655</v>
+        <v>0.7813900255892534</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9663035732464635</v>
+        <v>0.9399639213951474</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.8962438265594272</v>
+        <v>0.8373082433813508</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 75.45</t>
+          <t>X &lt; 75.39</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3613</v>
+        <v>3623</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.05631507812532277</v>
+        <v>0.04764395069057059</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6113461522638843</v>
+        <v>0.6247303471786267</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4248262708962258</v>
+        <v>0.4111569211251194</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.04578056153930987</v>
+        <v>0.06069364161849222</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1023011765624133</v>
+        <v>0.08202209882151834</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4148636179882885</v>
+        <v>0.3974758671851788</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4005986806851638</v>
+        <v>0.3795115361818873</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7500768379285958</v>
+        <v>0.7555122765162778</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7045450461734148</v>
+        <v>0.6788085779653201</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6995018014316088</v>
+        <v>0.6974988492363536</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.59346207725482</v>
+        <v>0.5917197903842322</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9201938691895677</v>
+        <v>0.9138194261647854</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.0415899889584</v>
+        <v>1.031084427209997</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.006515317483391</v>
+        <v>0.9923934660354092</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 79.54</t>
+          <t>X &lt; 79.47</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3676</v>
+        <v>3686</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.08075379868765964</v>
+        <v>0.07166703426413079</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6259022147966178</v>
+        <v>0.6119571689187637</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3815832315437078</v>
+        <v>0.3682611730517067</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.119748813748437</v>
+        <v>0.107142857142847</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1932574688423045</v>
+        <v>0.1739057014992653</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3970072301241601</v>
+        <v>0.3803729468205219</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4901395456118109</v>
+        <v>0.4699887177158502</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.879988993566819</v>
+        <v>0.8587345736072152</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8613945936006502</v>
+        <v>0.836922850382777</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8147561558689915</v>
+        <v>0.7870709608383635</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6526956608324994</v>
+        <v>0.6254211523588395</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.9472471793279027</v>
+        <v>0.915906343660474</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.004979876199265</v>
+        <v>0.9701714647160387</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9471615812624421</v>
+        <v>0.9092521920651819</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 83.63</t>
+          <t>X &lt; 83.56</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3733</v>
+        <v>3743</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1885981178906349</v>
+        <v>0.2055431271896921</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.5941462075099651</v>
+        <v>0.6071105573339892</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2941093976296898</v>
+        <v>0.3078585571565782</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.01150552249135472</v>
+        <v>0.02601728141296178</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1558370687776076</v>
+        <v>0.1642689827154555</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2540800572436623</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3712016883372442</v>
+        <v>0.3790707648320222</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7479558517010361</v>
+        <v>0.7547993096856302</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7821843154947317</v>
+        <v>0.7594101836434319</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7500317780258072</v>
+        <v>0.7244517597864615</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4534704151676863</v>
+        <v>0.428662980237192</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7172243146227544</v>
+        <v>0.6888574078415033</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8211623180754586</v>
+        <v>0.7896385110952053</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8479887478416188</v>
+        <v>0.8135408849103811</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 87.71</t>
+          <t>X &lt; 87.64</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3788</v>
+        <v>3798</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1631250112967493</v>
+        <v>0.1794709617831813</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.407897876401826</v>
+        <v>0.4211467854952176</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1064405216546831</v>
+        <v>0.1204816340656691</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.09124552116296059</v>
+        <v>-0.07668067226891395</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.01683453407518698</v>
+        <v>0.02621110145867078</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.06523906224872178</v>
+        <v>0.07694528110249621</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1793858315597561</v>
+        <v>0.1883392711833096</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5174994914311597</v>
+        <v>0.4992737562888436</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4975578944609182</v>
+        <v>0.4769210180658519</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5062118520715231</v>
+        <v>0.4830803354507793</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.263675414385375</v>
+        <v>0.241171926024208</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5768210127609521</v>
+        <v>0.5510245078344767</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6467222544232101</v>
+        <v>0.6182666588533863</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.6499915477220171</v>
+        <v>0.6190546211358523</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 91.8</t>
+          <t>X &lt; 91.72</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3839</v>
+        <v>3849</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2189801273057341</v>
+        <v>0.2086867250871265</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4391884502787278</v>
+        <v>0.4262656095116881</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.006632985153274262</v>
+        <v>0.02074512236784187</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1347725528656696</v>
+        <v>-0.1202939325510002</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.01670449378185879</v>
+        <v>0.0006790231597548768</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.009573246166716842</v>
+        <v>-0.02343795451567132</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1539192002462784</v>
+        <v>0.1375216638638364</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4033229084615471</v>
+        <v>0.3862859940725443</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.4088216743632671</v>
+        <v>0.3896575419993056</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4060585238107066</v>
+        <v>0.3848081268941641</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2420825874057755</v>
+        <v>0.2212558685184334</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4994513743848401</v>
+        <v>0.5018028429217409</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.5107406299840491</v>
+        <v>0.5109588574155595</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4908814529986358</v>
+        <v>0.4890276183690858</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 95.88</t>
+          <t>X &lt; 95.8</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3895</v>
+        <v>3905</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2058802847164216</v>
+        <v>0.1953501455060689</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2206698241878371</v>
+        <v>0.2084726421654892</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1601966010311529</v>
+        <v>-0.1713987063248581</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3745741010004551</v>
+        <v>-0.3852399197226788</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1818231637621963</v>
+        <v>-0.1708682372363199</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.177886716818854</v>
+        <v>-0.19078000342612</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.06925528285811566</v>
+        <v>-0.08416031901256105</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1441715921874049</v>
+        <v>0.1287463995735436</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1742903368142379</v>
+        <v>0.1570497090373735</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1592996285543009</v>
+        <v>0.1404081626677822</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.005324684279351288</v>
+        <v>-0.02378824579934502</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2487762343880391</v>
+        <v>0.2279134925178354</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3308018038375735</v>
+        <v>0.3080076867224477</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2630795643355341</v>
+        <v>0.2386940431916642</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 99.97</t>
+          <t>X &lt; 99.88</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3941</v>
+        <v>3951</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1493318197438498</v>
+        <v>0.163954774507566</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1198887693944855</v>
+        <v>0.1333071030785362</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1346467877054423</v>
+        <v>-0.1205453233953975</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2437655502875131</v>
+        <v>-0.2293973383344792</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1101277912782663</v>
+        <v>-0.09891725062003331</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.03963325371383775</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.02897195311626888</v>
+        <v>0.03981524857802299</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2091572354001201</v>
+        <v>0.2195913024016676</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1368619770341297</v>
+        <v>0.1460463188036201</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1374747870476938</v>
+        <v>0.1452981714290544</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.002267517604181535</v>
+        <v>0.005929143895556876</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2239094370551697</v>
+        <v>0.2300890424317785</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2747008659048973</v>
+        <v>0.2793483626471627</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2357639504296429</v>
+        <v>0.2390440412958412</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 104.1</t>
+          <t>X &lt; 104</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3981</v>
+        <v>3991</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.198102497257338</v>
+        <v>0.2121658973907401</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.177870328192455</v>
+        <v>0.1909978748684793</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.0530057728822797</v>
+        <v>-0.03925078641351831</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1847616195882154</v>
+        <v>-0.1706894704895277</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.08290784267258289</v>
+        <v>-0.07139199809478214</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.02248241417181873</v>
+        <v>-0.00996556904829049</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.03186817979020873</v>
+        <v>0.04307610083334623</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2557235747361801</v>
+        <v>0.2664295647855965</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1082901052344738</v>
+        <v>0.1181873172337973</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1254525172240761</v>
+        <v>0.1342223797868414</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.08545660403450483</v>
+        <v>0.09435211725291026</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.309729409065298</v>
+        <v>0.316871318700862</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3558116788707082</v>
+        <v>0.3616992993383619</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3446738122377013</v>
+        <v>0.3493720058676075</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 108.1</t>
+          <t>X &lt; 108</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4004</v>
+        <v>4014</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2201046316513597</v>
+        <v>0.2338663226173594</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.240567199110977</v>
+        <v>0.253457239982005</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.008767836603190915</v>
+        <v>0.02228987182878939</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.07164587348433571</v>
+        <v>-0.05793808577109161</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.05148620374423274</v>
+        <v>0.03802261786346151</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.08837828525409464</v>
+        <v>0.07582166592554529</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.06716479514113161</v>
+        <v>0.05362601642781328</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2621284304173841</v>
+        <v>0.273038999473556</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.09024866135325027</v>
+        <v>0.0756715494132294</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1273809063679892</v>
+        <v>0.111776452791247</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.03652742086809013</v>
+        <v>0.02117164702055874</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2596977530594771</v>
+        <v>0.267631763024248</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3280588259890393</v>
+        <v>0.3099270125480942</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2932996651589619</v>
+        <v>0.2990844692739998</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 112.2</t>
+          <t>X &lt; 112.1</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4031</v>
+        <v>4042</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1402511306921568</v>
+        <v>0.1409362638923</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.149797455921977</v>
+        <v>0.1494343262669844</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.03363253853630255</v>
+        <v>-0.03353565730153463</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1621420544456313</v>
+        <v>-0.161683824566353</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.04345276934569853</v>
+        <v>-0.04510836442408817</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.004842917688208104</v>
+        <v>-0.005705244707947088</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.05126879924993233</v>
+        <v>-0.05288445044747903</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1640086073592215</v>
+        <v>0.1617623786252196</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.007153590913134167</v>
+        <v>-0.009813181411615801</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.02401885723206476</v>
+        <v>0.02031949698165647</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06762224582204368</v>
+        <v>-0.07109382669391096</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1046674668498184</v>
+        <v>0.0998557848400381</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1697188045872267</v>
+        <v>0.163814040817357</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1614729208291195</v>
+        <v>0.1547356574582608</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 116.3</t>
+          <t>X &lt; 116.2</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4048</v>
+        <v>4059</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.09234178773700563</v>
+        <v>0.09303159358059787</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.09508999462842382</v>
+        <v>0.09487124716669371</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.03996540290852835</v>
+        <v>-0.03985245118308711</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1181072114873842</v>
+        <v>-0.1177720043534833</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.002160003145242229</v>
+        <v>-0.003717465154764454</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.03754459303686275</v>
+        <v>0.03667136680233796</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.01562957494979855</v>
+        <v>0.01404043199056559</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1540611541089021</v>
+        <v>0.1520571926405552</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.05737788829556933</v>
+        <v>0.05486119583681415</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.06019050927471881</v>
+        <v>0.0568243770532959</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0319161206336176</v>
+        <v>-0.0350517374212771</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1151121623098064</v>
+        <v>0.110810145284411</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.153431469285934</v>
+        <v>0.1482181498472599</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1461641919365348</v>
+        <v>0.140217002083233</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 120.4</t>
+          <t>X &lt; 120.3</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4064</v>
+        <v>4075</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1558266724335127</v>
+        <v>0.1562286839192808</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1522550893556911</v>
+        <v>0.1518786945571193</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.008345900991258759</v>
+        <v>-0.008319115684997769</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.0856616195513098</v>
+        <v>-0.08541703094946484</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.02138034359096963</v>
+        <v>-0.02268974540134394</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.005225970740198704</v>
+        <v>-0.005886665413491698</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.002834306445208767</v>
+        <v>-0.004179275997643117</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1332123912769063</v>
+        <v>0.1314655630535881</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1103925732359556</v>
+        <v>0.1080301011942382</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.06070010867135522</v>
+        <v>0.05773549881494944</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.007261205981073715</v>
+        <v>-0.01005903601451053</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1393298543418879</v>
+        <v>0.1354648212744323</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2004508083358232</v>
+        <v>0.1957147296100885</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1941124350662236</v>
+        <v>0.188734497854945</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 124.5</t>
+          <t>X &lt; 124.4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4071</v>
+        <v>4082</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1635501790640745</v>
+        <v>0.1638808491056949</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1082407615352992</v>
+        <v>0.1079812413982992</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.003776987040140511</v>
+        <v>-0.003762788902378134</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1052393963747562</v>
+        <v>-0.1049434436531271</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.04199674138995846</v>
+        <v>-0.04316540313021733</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.02536481982635053</v>
+        <v>-0.02592921766215994</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.04764943140531841</v>
+        <v>-0.04878934766492193</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1118785951086707</v>
+        <v>0.1102764910761991</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.08898800421062703</v>
+        <v>0.08681265899347324</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.06245554237206363</v>
+        <v>0.05966148410042393</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.05483209124736277</v>
+        <v>-0.05732582806163578</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1161063638114115</v>
+        <v>0.1125225231960911</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1763942809336214</v>
+        <v>0.1719860496697834</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1704490448875617</v>
+        <v>0.1654390484331216</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 128.6</t>
+          <t>X &lt; 128.5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1647801411310965</v>
+        <v>0.1649854513776106</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1274100715237765</v>
+        <v>0.1270954246689087</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.0874129029666193</v>
+        <v>0.08718234738454811</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.0374682769171315</v>
+        <v>-0.03735702117303674</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.0255212715339681</v>
+        <v>-0.02652831747160889</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.03213420072546569</v>
+        <v>-0.03257896527536985</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05467961989700854</v>
+        <v>-0.05559720074680286</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.07781880877048053</v>
+        <v>0.07651855662081886</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.005897771646687033</v>
+        <v>0.004257598040929622</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.02480014413877996</v>
+        <v>0.02253024207021781</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04397213512158515</v>
+        <v>-0.04607060849831157</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1264013651230442</v>
+        <v>0.1233175300755178</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1357826634885697</v>
+        <v>0.1321181858919473</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1307909410064099</v>
+        <v>0.1266214880979675</v>
       </c>
     </row>
   </sheetData>
